--- a/results/HeC_GSE14323_13_5_5.xlsx
+++ b/results/HeC_GSE14323_13_5_5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="78">
   <si>
     <t>classifier</t>
   </si>
@@ -70,60 +70,60 @@
     <t>log_loss</t>
   </si>
   <si>
+    <t>POM_ALG</t>
+  </si>
+  <si>
+    <t>RND_FST</t>
+  </si>
+  <si>
+    <t>POM_enGROUPS</t>
+  </si>
+  <si>
+    <t>BAGGNG</t>
+  </si>
+  <si>
     <t>POM_ENTROPY</t>
   </si>
   <si>
-    <t>POM_ALG</t>
+    <t>5NN_MUL</t>
+  </si>
+  <si>
+    <t>5NN_OVR</t>
+  </si>
+  <si>
+    <t>3NN_MUL</t>
+  </si>
+  <si>
+    <t>3NN_OVR</t>
+  </si>
+  <si>
+    <t>1NN_OVO</t>
+  </si>
+  <si>
+    <t>3NN_OVO</t>
   </si>
   <si>
     <t>7NN_OVR</t>
   </si>
   <si>
-    <t>POM_enGROUPS</t>
-  </si>
-  <si>
     <t>7NN_MUL</t>
   </si>
   <si>
-    <t>RND_FST</t>
-  </si>
-  <si>
-    <t>5NN_MUL</t>
-  </si>
-  <si>
-    <t>5NN_OVR</t>
-  </si>
-  <si>
-    <t>3NN_MUL</t>
-  </si>
-  <si>
-    <t>3NN_OVR</t>
-  </si>
-  <si>
     <t>SVC</t>
   </si>
   <si>
-    <t>1NN_OVO</t>
-  </si>
-  <si>
-    <t>BAGGNG</t>
-  </si>
-  <si>
-    <t>3NN_OVO</t>
+    <t>5NN_OVO</t>
+  </si>
+  <si>
+    <t>1NN_MUL</t>
+  </si>
+  <si>
+    <t>1NN_OVR</t>
   </si>
   <si>
     <t>7NN_OVO</t>
   </si>
   <si>
-    <t>5NN_OVO</t>
-  </si>
-  <si>
-    <t>1NN_MUL</t>
-  </si>
-  <si>
-    <t>1NN_OVR</t>
-  </si>
-  <si>
     <t>MLP</t>
   </si>
   <si>
@@ -139,133 +139,109 @@
     <t>A7</t>
   </si>
   <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
     <t>A5</t>
   </si>
   <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
     <t>A10</t>
   </si>
   <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
     <t>A8</t>
   </si>
   <si>
     <t>xuyager</t>
   </si>
   <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f22bb50&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82c51d550&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f1e6e50&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c4f0550&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f847f50&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f847850&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f847550&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f847990&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f847510&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f847490&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f847410&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f847210&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efb063310&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0ef9596ed0&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efab9e750&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef9af5890&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efab9fc10&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efab9ef50&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efa134510&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efab9eed0&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efab9ead0&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efb889e90&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efa123110&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efab9e850&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9244b06e10&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9243f8a3d0&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f925083fc10&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9243fb1690&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f925083c490&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455bff10&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9243f89690&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455bfc10&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455bfb90&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9243f89c10&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9243fb4a50&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455bfa10&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd2df3d10&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd21b8690&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd3863610&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2dd5350&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd3863690&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd3863d90&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2dc2510&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd3863850&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd3863250&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd3863050&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd3862850&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd3862c90&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b81915050&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b5b4910&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bbb7d50&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b5b6e10&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbb7890&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbb7490&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bbb7d90&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bbb7990&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bbb7410&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bbb72d0&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bbb7210&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bbb7010&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f263e90&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f1a5910&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f8bcdd0&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c524190&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f849890&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c503190&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f8bac50&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f201b50&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f203a10&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f202650&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f201f90&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f202890&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bc07ad0&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bc06a90&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bbf0950&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbcd190&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b781afa50&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b781af750&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bc05e10&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b781af850&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b781af8d0&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b781af610&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b781ae190&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b781af310&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd55b790&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd2dc2990&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd563950&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd5c77d0&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd224ae90&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd224bfd0&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd562510&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2249f50&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2248290&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd2dfd0d0&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd224b350&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd2248ed0&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9245631890&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9244b554d0&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9245636f90&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f924422f2d0&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455b1610&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455b0890&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455b1690&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9243f9ad90&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9243f995d0&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455e1c10&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9244b14a50&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9243f99f50&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0ef9af4210&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac42d90&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac03950&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efac40950&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efac2f650&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efa14d690&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef97d4510&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef956c850&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef956d250&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f049530d0&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efa1323d0&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0ef956c890&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92455f36d0&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9243ee56d0&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9243f67c90&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9243fb9650&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92456260d0&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9245634950&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9250832c90&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9250830890&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455da0d0&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9244b49c10&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9243f4ca50&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455db890&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd3852450&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd21fb750&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd2233b10&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd38b2210&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd21f4210&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2214850&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd21fa510&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2216d10&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd38d2690&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd224d0d0&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd38d0790&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd38d1410&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f241d90&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f877a50&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f89a690&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c53c190&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f8c2b50&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f8c1b90&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f85c950&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f85d650&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f85ff90&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f85ff50&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f85d510&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f85ced0&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b81948d90&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b582190&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b8191f050&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbf5190&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b781ca0d0&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b781cabd0&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b781cab10&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b781cb3d0&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b781cb210&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b781cbf50&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b781caa90&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b781c9dd0&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efa149cd0&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac3b250&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0ef95b4210&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f0490c8d0&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef9572d90&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f0478fa10&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef95b4510&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f0478c5d0&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f0478ce90&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0ef95a30d0&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f0478c0d0&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f0478ea90&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
+    <t>{0: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb8395cf710&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82c556e50&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f21f7d0&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f20c290&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb8395a9690&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb8395c00d0&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb8395c0290&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb8395c3d50&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb8395c2c50&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb8395c1e90&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb8395c0b50&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb8395c3fd0&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b78189b50&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bbdd690&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bbea190&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b8194d190&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbf9910&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b5e8cd0&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bbfde10&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b5eaa50&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b5ea750&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b5ea250&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b5eaf10&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b5ebe10&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efababfd0&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efa148d90&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f0478c310&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef95c0710&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efac18110&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efac349d0&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efabc4510&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f04797650&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f04795690&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efac0b0d0&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f048f21d0&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efa122a50&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9244b01890&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9245618890&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9243f509d0&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9246209190&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9244b5e190&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9243f84d90&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9243fb9490&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92507ec310&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92507ec950&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9244b61c10&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9243f84a50&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9250827f10&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd38d3650&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd38abd10&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd3d9750&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd21f8b50&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd597c10&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd597050&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd38aa510&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd597ad0&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd597a90&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd58d0d0&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd5979d0&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd597850&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac24210&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f0478c8d0&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f04786d90&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efa145690&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f0476cfd0&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f0476f790&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f04785810&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f0476d810&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f0476cb10&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efac4a1d0&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f0476e110&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f0476c150&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f925080a250&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f925080ca50&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92455dc150&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455f2610&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9243f74d90&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455dde50&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455de9d0&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455dc950&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455de110&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455dd810&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455ded10&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455de250&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd5a3650&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd5a1950&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd5cf910&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd5a0190&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd5cfed0&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd5cd790&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd5ccdd0&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd5cef10&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd5ccf50&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd5cfb90&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd5cc490&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd5cd710&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bc5a550&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bc4c250&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b59b9d0&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bc4d190&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b598a90&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b598390&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b599a10&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b59a410&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b599f50&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b59a050&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b59b5d0&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b59bdd0&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb8393dbe90&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb8393fcfd0&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f87a950&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb83956c190&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb839589a50&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f8b8f10&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f8b9650&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f8bb390&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f8b8e50&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f8b9690&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f8b9490&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f8bb490&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
+    <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.6050591781005384, 1.2319737970876001, 0.6947364870418778, 2.5245078344934115, 0.6940985858502591, 1.921664582300038, 1.2499151482274942, 0.5408266683156078, 1.9754336740787968, 1.809926123628488, 1.2949101865812318, 0.6289568380189718, 0.6392249802744533, 0.5498638681852921, 1.196194016243431, 2.6918305284386377, 0.6556115488960418, 0.5943306020717929, 1.2611403028600365, 1.2141405379419319], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.5980612896953622, 0.6175049296758347, 0.6412997478212316, 0.6453802537714955, 0.6260348118832086, 0.6790924760548036, 0.6573193791290942, 0.5411223364484777, 0.7306046238456378, 0.5906546731378158, 0.6587442753344066, 0.5893739319137711, 0.5999898585992879, 0.6181708514236965, 0.6778328008252065, 0.8018805556142918, 0.6779956345327377, 0.6291854230838315, 0.6386883747055502, 0.5853401123630352], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.6305223054601229, 0.5911987008466582, 0.62877383675511, 0.642516369035209, 0.6182374462504397, 0.684362351695599, 0.6463801996794482, 0.5755891215273095, 0.7018762096285002, 0.5834913254345345, 0.6544199185804617, 0.583288462638876, 0.6054092174659339, 0.6286625382038232, 0.7004082791950731, 0.7505817697365346, 0.6501375593356, 0.6154802372936947, 0.6140292064457438, 0.600542403581413], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.2004235215815227, 8.884229915464964, 3.6536058235166777, 2.792070397396038, 2.380970724664281, 0.6680220463915906, 3.1325101502154657, 2.0941094556669615, 3.248886761751654, 1.0112153457258708, 3.411649338622619, 0.3815202509521732, 0.26699402560624985, 1.0891329653214221, 3.474927330291631, 1.6900222461658054, 2.0176057370366567, 1.5251174652888562, 2.0078762632073843, 1.6145695741918609], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4899738953155915, 0.27878204422370556, 1.7834178088426935, 0.5587296160717831, 0.30235984097565566, 0.6011803828564103, 0.5221553854388237, 0.2847420166990177, 0.8112065735353094, 1.7847402932841148, 0.4868283146362215, 0.4515143219147994, 0.33198190217854784, 0.2512338065557157, 0.7942831684465601, 1.8154940303321456, 0.6644542257391622, 0.2917409588750631, 2.873450922160774, 0.4409249646891808], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.49662780151572367, 0.29409454756487535, 0.251693849202729, 0.7346885455183217, 0.3658372986740333, 0.7052947665611977, 1.6678355407264553, 0.3112662379401059, 0.8783940694093371, 0.3898146498796358, 0.5863413747784385, 0.3890390887409703, 0.2938575558947449, 0.24883180608509706, 0.7415753883597357, 0.538114741767272, 0.7370341989756247, 0.29403075841859966, 1.9588290308097653, 0.3337432657128921], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.6080497462833169, 0.4669238320851636, 0.4614723478489479, 0.630841831918187, 0.49054852483418704, 0.5663937628819581, 0.5205187931712182, 0.4551367939877674, 0.633001987413747, 0.4641565723516814, 0.5406487973148723, 0.5440147406963516, 0.49560262472474104, 0.4482804924211553, 0.6279184161294312, 0.5971648194295629, 0.5914328760340103, 0.5185213335388846, 0.42310410223305295, 0.5028461306653633], \'SVC(C=1, random_state=13)\': [0.6557179725030083, 0.5713872985153203, 0.646204104755914, 0.6739564462555552, 0.6790932365761714, 0.6782676498235963, 0.6825113063039885, 0.6162622687943266, 0.737857992572326, 0.6214861311341566, 0.7029434241357928, 0.6588146751738413, 0.6974213351444095, 0.6471831501291069, 0.7386635943471183, 0.7302082915778704, 0.6487316081818317, 0.6398781368706563, 0.6987702661254228, 0.6070938597012484], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.610569640845848, 0.46697048740578095, 0.4642346268989686, 0.6358336224250344, 0.4950517200538323, 0.5693560336144821, 0.5414038983439584, 0.45750918625761755, 0.6521101828944103, 0.4630773951569555, 0.5616689986968664, 0.5213339699271117, 0.49939036248220436, 0.46883194486362934, 0.66735809871395, 0.5974606839381279, 0.5930703225755749, 0.5207695697344478, 0.44269387819168166, 0.5225509672328033], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [5.792730008965258, 5.242713220235222, 5.792730008965258, 7.20873067782343, 5.149093341302451, 5.242713220235222, 3.218183338314032, 3.932034915176417, 7.723640011953677, 3.932034915176417, 4.505456673639644, 8.519408982882236, 4.505456673639644, 7.8640698303528325, 7.08000334429087, 7.20873067782343, 7.723640011953677, 4.58737406770582, 3.8618200059768384, 9.830087287941042], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.7761065990889264, 0.3640752418312204, 1.6107482602511964, 3.5313835574399595, 0.362711078092302, 0.9804124202479467, 1.5745460184558244, 0.9404628824781975, 2.8059990354027065, 0.9499764850920982, 2.834960828839004, 2.2489996777977956, 1.4785589040328933, 0.9825539299871537, 2.19225480405368, 2.856069636025682, 3.424880446616943, 0.4018832698617629, 1.530172685423896, 3.6112826329794583], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.635561599689572, 0.46716192477830604, 0.4643804368192129, 2.4022270931284533, 0.4999373384964442, 1.0995574360940883, 1.0961667617559756, 0.44452929207201153, 1.6607403655420223, 0.42198180387306955, 2.288014698707076, 1.6971989362154263, 0.9830047245777085, 0.4519865294540578, 1.0947088333802522, 1.808933238567794, 3.517384599184733, 0.4933353588808278, 1.6254889186487722, 0.532316814568417], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.5950533259321455, 0.5942454575644406, 0.6626686791902312, 0.5983836012310513, 1.165153188437105, 1.3823263894955113, 0.5979651005843957, 1.2810620413402913, 1.330866363538508, 0.603469308554735, 1.8151590515273885, 0.5906929256693001, 0.6272749435532458, 0.6558724902036802, 1.9373627076019384, 0.6706847198958825, 0.7183426267260303, 1.295265198263197, 0.6605896448202028, 0.6896989808783283], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.5921370824948001, 0.6183853509946483, 0.5979970036262106, 0.6054870587551767, 0.540743486856442, 0.6645170635663474, 0.5775881461146396, 0.6630521713802927, 0.6402247189133716, 0.6630856105830878, 0.6225306967876686, 0.5849243692111383, 0.6170224003189466, 0.5937986791571179, 0.6706640881539511, 0.6298255680995986, 0.6484165752310472, 0.725662384414053, 0.6228668148191302, 0.6522436051272874], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.5877762881609315, 0.6140588597844965, 0.5772221573212839, 0.6163449353238096, 0.5427190770696756, 0.6469674301059815, 0.5630171655242698, 0.645466836354482, 0.651243214024155, 0.643766778888039, 0.6087676863995986, 0.5975362872545673, 0.5931961937575332, 0.6053090990573025, 0.6297023419931972, 0.6228247844566237, 0.6407798180656694, 0.6976641388063276, 0.6307182913078441, 0.6130637424899721], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.564168969802726, 3.604510501922391, 0.2331064617261807, 10.38974982835143, 0.16849146577092516, 6.21979984044454, 0.28880261455801953, 2.667884687224297, 1.0392899851446196, 7.459610007587962, 1.7706131084509273, 8.879344486135743, 0.411903269515227, 8.911974778087554, 1.4202916188926693, 0.3608452720588002, 0.4509469484909731, 6.217388405532686, 1.2202214527940263, 3.0782033501820614], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4830698328723697, 0.2640697497509802, 0.23683176595074545, 0.42936048286065315, 1.8784455127194437, 0.3950667843856559, 1.7826410476667245, 1.199138287582268, 0.20901005684172366, 0.448367257259174, 1.4909110053321055, 0.35736422709731397, 0.5611554833026547, 0.24915837102651994, 0.2910526270437673, 0.3688627400865086, 0.4289819890456132, 0.453384722366699, 0.36464372141467255, 0.3669352179613977], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.7002873052046285, 0.30026012796912727, 1.5292001514949511, 0.5393317183391716, 0.27836070440199384, 0.4944599209041011, 0.8569699235692586, 1.4857576076760932, 0.2063152249097015, 0.5014421810088912, 0.42847163764455354, 0.37702640876089805, 0.4358111541570238, 0.23185883022012002, 2.3318561888236866, 0.31151259796738756, 0.4389144635636851, 0.5975476297731271, 0.44374575426963647, 0.4086946051030441], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.5768158311410201, 0.4778035378942525, 0.46380209936431605, 0.5226564025348023, 0.4348816054456274, 0.5258952923787116, 0.4361575968461539, 0.5814404856622875, 0.4476128864998127, 0.498901361752195, 0.5440522013062588, 0.4908260298750802, 0.49748662371777236, 0.54358939541349, 0.49341860726371617, 0.4503964756517568, 0.5609088612581589, 0.49456296688604706, 0.5625881687504131, 0.48130184871522286], \'SVC(C=1, random_state=13)\': [0.6385227066700983, 0.7297906968737603, 0.6074107758043564, 0.648105769471157, 0.6372770337889669, 0.6505212433459776, 0.5935924669400107, 0.7080822572851815, 0.6411198538119225, 0.6840889324110926, 0.6742416349798567, 0.6325196192253189, 0.5429719606681662, 0.7021731457542909, 0.5790722379881521, 0.6829550599817785, 0.7186811172721589, 0.665755411565831, 0.6785340638940959, 0.6319780555542794], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.5780625536435041, 0.4821035266408717, 0.46610709512309534, 0.5402334906864729, 0.4354132675441556, 0.5277645206379041, 0.4029642424834145, 0.606215429222748, 0.4670187530506766, 0.49887480768084314, 0.5481516773557489, 0.49109894363026135, 0.4811562214972973, 0.5265211924791717, 0.49302098134988565, 0.47210648252888326, 0.6008981031765923, 0.49531321303580766, 0.5645272080150335, 0.48176196471833865], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [6.4363666766280625, 4.58737406770582, 5.792730008965257, 5.898052372764625, 2.5745466706512263, 6.553391525294027, 1.9309100029884194, 5.898052372764625, 7.08000334429087, 5.242713220235222, 6.4363666766280625, 5.898052372764625, 3.218183338314032, 6.553391525294028, 4.505456673639644, 3.276695762647014, 6.4363666766280625, 5.242713220235222, 5.792730008965257, 4.58737406770582], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.8627499966589194, 0.9825539299871541, 0.34402364438642524, 1.5979435447468069, 0.9082573628383129, 1.6336100630381423, 1.544653582142045, 1.6409821559128361, 0.9650083240945262, 0.973040327373253, 2.1747399959641847, 0.37976699123768126, 0.8636420470674853, 1.6400345922557635, 0.8627114041900027, 0.3398174534679318, 0.9360465306582285, 2.9454823141790816, 2.1955306981639255, 1.0225034677569032], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.663774276913369, 0.468766562010213, 0.3684134744209207, 0.46685091627097985, 0.36356159731505205, 1.0739208744988662, 0.4034430905999109, 1.7228560162357351, 1.1034072101150498, 0.37702754696780694, 2.245946312858632, 0.4326688341440172, 0.3429292537844896, 0.4623625512176794, 0.3368412790171575, 0.44292465484010446, 0.4520028085949282, 1.1234486409647817, 1.7020596351779655, 1.069206645445592], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.2674258742177926, 1.9564515808771146, 0.5955010694598618, 0.7469544316712521, 0.6605302548743175, 1.3030843875308467, 1.2042470528600882, 0.5719767289488243, 0.6192375100615032, 1.9536412670641605, 1.2290576171553464, 2.4814087535642986, 1.3032046066092842, 0.7151747798436521, 1.2972819626371237, 1.2688342614610695, 1.8528819684716946, 1.860704149620439, 0.7585336568940665, 1.993142494694512], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.6494811043969752, 0.6667103115085131, 0.5940087876485582, 0.7239109522784581, 0.5847551421969731, 0.6166508709549104, 0.6842009608878762, 0.6117758983155395, 0.6010851992911883, 0.7054568526639422, 0.597289689287295, 0.6181822290756517, 0.6007357407815466, 0.6746093112463601, 0.7376272241432564, 0.6182145927920091, 0.6564942980249838, 0.6240013862596683, 0.7006884790934417, 0.6852324714758816], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.6315882093278837, 0.6426231847033248, 0.6038988120097171, 0.6948649235359856, 0.5697486606379728, 0.5988991526055285, 0.7064417134754256, 0.6079920067342539, 0.6102260955590043, 0.6712653085931691, 0.6155371387419433, 0.5971043227939518, 0.6129644410684844, 0.672817064174635, 0.703107825957672, 0.6154047314290095, 0.6291677487701456, 0.6027848962480785, 0.6496961324348683, 0.6952499968479126], \'MLPClassifier(max_iter=2000, random_state=13)\': [0.4174245992679203, 1.1230936809507073, 0.394029634369545, 3.4819597627093652, 3.171915410801443, 4.462591654903584, 0.5980167489308397, 2.223071382816178, 0.1908137670729019, 2.278656967877158, 0.4815980282152026, 5.093384243196218, 0.3676289333431102, 1.4000297051262398, 1.8164587845009372, 5.647375898164342, 0.47415182299907094, 2.314407295293441, 0.3427611466909405, 2.5094846478301633], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.38208077686182135, 0.5317196152223668, 0.32492916186580506, 0.49979743344273686, 0.23890220375168106, 0.35458051844889366, 0.7282866726385283, 0.5850500844060531, 0.18121868133091676, 0.553883923899072, 0.41395599574032227, 0.3357861241331943, 0.47074145793020694, 0.24890877687257693, 0.60910160609313, 0.3146261674120212, 0.5728258351097999, 0.34112494011866573, 0.3169549473740842, 0.593207974328024], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.38579768780608487, 0.5549572030159454, 0.4737755050991997, 0.5397386630370116, 0.3116347479842399, 0.43539828845091494, 0.7283676170345286, 0.5666351371032301, 0.18100382170302032, 0.3812875989353428, 0.47584356045422893, 0.37658774664647837, 0.44183476185689957, 0.28846830471388296, 0.7056898702052555, 0.39548424132154103, 0.5098528634832872, 0.40507355012922935, 0.30475320395786654, 0.5576581826743052], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.47908147748886926, 0.6495672655740791, 0.5179911815605305, 0.5879727992476373, 0.45000827279812255, 0.4630884519974514, 0.6529136529976848, 0.5779221056766536, 0.38496069698761687, 0.48237385522747767, 0.4773599805538611, 0.4797533125523394, 0.47809438906175084, 0.43105429389158406, 0.5426073426842244, 0.5420485752022142, 0.5958937779699306, 0.55364477660307, 0.4800307030424982, 0.5481158338868095], \'SVC(C=1, random_state=13)\': [0.5655754183885972, 0.6947953385759853, 0.6043059530096981, 0.7326382579001808, 0.5658822467351343, 0.7049963334068812, 0.7093102788819845, 0.6640525251170637, 0.5516355436885909, 0.6933465042604865, 0.5868001134946425, 0.6667071426985952, 0.5501761457856313, 0.7464222885121684, 0.6409958718283691, 0.7362217854960809, 0.6346331058834959, 0.6929401318642213, 0.6300499502088116, 0.7322852508964433], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.47955953058573464, 0.6538886118131105, 0.539563159977188, 0.5863833221322952, 0.45311221052689854, 0.5017253718349886, 0.6953378630185296, 0.5605196563321964, 0.3856074027424455, 0.4851705347605142, 0.49676288000051366, 0.4810544413186649, 0.5165955169493973, 0.4503768120134966, 0.5207313715837641, 0.5273291321486092, 0.5961892734602369, 0.5548801578823761, 0.5234587722035183, 0.6046464592041947], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [5.792730008965257, 5.898052372764625, 5.792730008965257, 5.242713220235222, 8.367276679616483, 5.898052372764625, 7.723640011953676, 5.242713220235222, 4.505456673639644, 3.2766957626470146, 3.8618200059768384, 4.58737406770582, 6.4363666766280625, 5.242713220235222, 5.792730008965257, 4.58737406770582, 3.8618200059768384, 3.932034915176417, 5.149093341302451, 3.932034915176417], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [1.5332065967952424, 3.477637397577896, 0.9257721709278081, 2.1669590925190896, 1.581786466814899, 2.233307928391335, 2.7761065990889264, 2.1890753711431716, 0.8823294807733617, 0.327214777457751, 0.8699518525490769, 1.6357515727773495, 1.5425503136481808, 1.0802862646723206, 0.9804198636901571, 1.5831993589974191, 2.8059990354027065, 1.5789163395190051, 1.5796831983210349, 2.239486075183895], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.0040807295367908, 2.973093660557704, 0.47568921552147636, 1.0274821814292308, 1.041415292899266, 0.4797646007884867, 2.314006052817109, 2.3299259744636216, 0.39316873086949017, 0.4493286656326382, 0.3400970211027638, 1.1252996606217496, 0.4609230160439859, 1.1264730882787963, 0.4636514726313513, 1.091754133644534, 1.6708130465828224, 1.0434849393430177, 1.0447748110792325, 1.6711662216055256], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.7565726771439378, 1.2875546145007268, 1.2284357858891704, 0.6133502331198636, 0.700752358765207, 0.6812831877989284, 0.794862117507731, 1.3198252072076382, 0.6149727752002893, 0.5867284888779434, 1.3371411391424173, 0.5498075547413905, 1.2300711588306787, 0.6078367340818689, 0.6353866448439172, 1.1744202820327059, 1.8461560925127436, 0.5021802856552459, 1.2410117359757504, 1.2242268080819472], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.6593371137966366, 0.6992447047035061, 0.686294609882622, 0.6607216942003079, 0.6491685727203961, 0.5975821535493266, 0.634813610986744, 0.6660131776665484, 0.6180016651262995, 0.5902515011656666, 0.6064838381936904, 0.6088817930371289, 0.6298397883907668, 0.6318664618527489, 0.6421268652467467, 0.6052914041614385, 0.6123509335645485, 0.5414679589312772, 0.6056073919771535, 0.6248476196920552], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.6492590768512494, 0.6697468481584005, 0.6874974638655197, 0.6525172162168488, 0.6280730388702789, 0.5891755176292504, 0.6538427784697965, 0.6428097486862336, 0.580240993437286, 0.5823471158293849, 0.6094038336102535, 0.5922630395900844, 0.6107596916221956, 0.603249297322292, 0.6201258868551653, 0.5694467090553944, 0.6376035726017248, 0.533881179242668, 0.6177144665850905, 0.6081960998199265], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.1877351493210244, 3.0358890442157707, 0.5999429027072026, 2.9828876288695514, 2.1174577937275485, 1.6687151958297939, 5.969142171485283, 7.502268123087099, 4.835690271811283, 1.8022389509084948, 8.430465254469516, 6.538055997664123, 3.6376796871910315, 4.679339674444174, 3.7585936647555656, 1.091933957837066, 5.5429453286275026, 1.7818673163579724, 5.428855078648213, 1.8746458069173637], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.36803466555728875, 0.41889126097290247, 0.5748479015051586, 0.6099137168730207, 0.383668620499972, 0.2777354517697968, 0.4285353397300432, 0.6245633328219878, 0.3770015963123803, 0.23319379839692667, 0.3295755220310029, 0.38484142954962225, 2.1818352519493276, 0.2942473796480529, 0.40283695078007087, 0.2985544564742283, 0.37378766114529915, 0.21495747404746385, 0.2721285669833187, 0.33654366159740223], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.0525055106434333, 0.3979237422081987, 0.7189357418887311, 0.5538753033645574, 0.511539827379849, 0.27641913148879177, 0.34632377990580165, 0.8162506609071652, 0.3449822251946321, 0.30280052435172405, 0.21425850708318725, 0.43979317274589075, 0.3230197168815934, 0.3130497412046773, 0.4038448649872238, 0.41474465562464574, 0.5763971536143541, 0.23495682403096085, 0.3147942018741971, 0.3876186389191358], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.4661669440771566, 0.5591859310231162, 0.5026084135423063, 0.6033369552936604, 0.4961792450995236, 0.4845009495746922, 0.46151793479306896, 0.6548261106989484, 0.4977680643306431, 0.4957880421416259, 0.47824717648554105, 0.5265993135327358, 0.4986522692516981, 0.4270880876636148, 0.4639531251756364, 0.461810040625106, 0.5193304958876189, 0.4435839274364308, 0.46421483135252845, 0.5036148442056072], \'SVC(C=1, random_state=13)\': [0.6442707493116266, 0.5702535759099725, 0.6899989480976931, 0.611231385614008, 0.6627435970572392, 0.558934468059458, 0.6636319621559288, 0.6490204749220088, 0.5763138980738028, 0.6069093152964934, 0.6011604767037816, 0.5729020376630275, 0.6364593001412865, 0.6268867480242885, 0.7221863141381267, 0.5652923979961276, 0.700823313448691, 0.5706495062610117, 0.6316992953328933, 0.5538485382798997], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.49448359369692285, 0.5810347183433995, 0.5392811129962735, 0.624693438840617, 0.5148486337968349, 0.4840725366924367, 0.46222739582031386, 0.6569065017205932, 0.4807102609238515, 0.5185415943933723, 0.46085974982762895, 0.5675046102660373, 0.5173108254361839, 0.4667295562955305, 0.4811292688707969, 0.4961744380095281, 0.5188093717344624, 0.4432677950353461, 0.46448519784507475, 0.5061927268038737], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [7.723640011953676, 4.58737406770582, 5.149093341302451, 7.8640698303528325, 3.218183338314032, 6.553391525294027, 3.2181833383140317, 11.140765592999847, 2.574546670651226, 5.898052372764625, 5.792730008965257, 3.276695762647014, 5.792730008965257, 6.553391525294027, 5.149093341302451, 4.58737406770582, 5.149093341302451, 5.898052372764625, 3.8618200059768384, 5.898052372764625], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [1.6717057584951376, 1.597943544746807, 1.5507214048847378, 2.9454823141790825, 1.476455635539029, 1.7021004086495943, 0.9330126192868823, 4.224530737999904, 1.4722490985513015, 0.9373738090819175, 1.5745460184558244, 1.0194143943606233, 1.5507214048847373, 1.0046702086112353, 0.9360465306582286, 2.240680021266029, 1.59719800641053, 0.9121684570615558, 0.8989136459853745, 2.25637177067249], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.4757093675461156, 0.43812528127947786, 1.0425879185156475, 1.124416723046942, 1.6007135101755636, 1.1577363860241838, 0.44896889722358185, 3.6812755169492757, 0.36117302606184637, 0.44815523797559137, 0.4024922956977893, 0.4603061859858247, 1.0700372010014039, 0.4547645943430116, 1.000096023263323, 0.476449663392233, 1.122498001200168, 0.42818046909071666, 0.44150661815024755, 0.49088284063429466], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.225619156332359, 1.3227652484729333, 1.8798868642570599, 0.5507433878995505, 1.8480260092666294, 0.6519396921119561, 1.1631253798145695, 1.9038100662706507, 0.5763232974776973, 1.3453978811792273, 1.2677948010468558, 0.5768117692940006, 1.2234416200395664, 0.5330028474409665, 1.2512415836133293, 0.5638658358524934, 0.6477527520424836, 1.3033912397189908, 0.6277260439082873, 0.7713646700260753], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.6367434368248625, 0.6276095147871399, 0.685007830702811, 0.5882959577351276, 0.58324671297026, 0.5929195193282563, 0.5841414349053838, 0.684119786980081, 0.5966850763428484, 0.7165235092920318, 0.6607379270908326, 0.5911145965596347, 0.5860653891404422, 0.6019478769611167, 0.6289448650026677, 0.631532646567673, 0.5673198429106326, 0.6025954134496764, 0.6066098546514668, 0.6695080255415949], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.5973675922890267, 0.602043745742848, 0.69738224264057, 0.5740404717718165, 0.5898469780212967, 0.5965723550369632, 0.5989938341177089, 0.6691377710238521, 0.5726822275134041, 0.6940490004790972, 0.6356927955088089, 0.5563705243095141, 0.5933121901677376, 0.5943214169194879, 0.645855100667117, 0.5965466937245523, 0.58427630872195, 0.5909032531963722, 0.6111942679750072, 0.6614335108163332], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.1864235140820316, 2.2236396213489056, 2.078355172626382, 0.26113032846161505, 1.700250244939967, 2.897660546819197, 2.1870899671650403, 1.544585566871323, 0.23739275949310773, 4.464295129063591, 3.841789015322913, 0.13950099461508747, 5.958472826588951, 1.159693515247938, 3.476192208450782, 0.20685189232306228, 2.260152217691126, 0.2159977659904755, 2.086562952001466, 0.7774922926321765], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.30418774253813063, 0.2003702783028071, 0.7894832783673035, 0.2373013866204567, 0.18662081516521414, 0.38377645840435365, 0.6668321179252562, 0.5178543761893151, 0.203006392088793, 0.6675461342297468, 0.43130768529330954, 0.14039221217202097, 0.3693715330094986, 0.18837497527148056, 0.467528281601183, 0.21508863112041424, 0.2638301122282587, 0.25631173990686523, 0.3724141720423919, 0.7173181940969249], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.3918243882887987, 0.1747053057879002, 0.8094979594534405, 0.27075075008328237, 0.2654243049447243, 0.3937498048190377, 0.6776783979060441, 0.5017816249953282, 0.21664354032862457, 0.6284171113852757, 0.5081438070545802, 0.11984293605235494, 0.37472379579431825, 0.19614561674485997, 0.5557188907611905, 0.23672081902050926, 0.22878916363761403, 0.22141392127691462, 0.21135758164667084, 0.7135710459373474], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.46676837233366114, 0.4445532416338193, 0.5673202306589488, 0.4261525072388276, 0.4608023079709996, 0.4777843868028735, 0.5636163902220382, 0.5897617431415291, 0.42706112854943507, 0.6360205147205775, 0.49860903776273396, 0.42032581224615534, 0.47979559034148883, 0.44108642447776075, 0.5284627720228928, 0.4431764715652437, 0.4244009171940196, 0.49901708713716486, 0.4775173423181017, 0.5832511529571291], \'SVC(C=1, random_state=13)\': [0.6772853526377779, 0.533880960757025, 0.6308896574283039, 0.6060855576389061, 0.6643663434078683, 0.5685441538058696, 0.6803286263320947, 0.6754991227862408, 0.643644389139393, 0.6280771837923425, 0.6779355744811918, 0.6441307107032466, 0.6635625907246571, 0.5045327188174663, 0.6572819766655922, 0.5243006317854162, 0.6044636427059051, 0.5997911227443139, 0.6157584687049502, 0.6051276774253985], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.4331499086854627, 0.44717810024030263, 0.5554926347906591, 0.46268894206174715, 0.4748645192173798, 0.47934364595517037, 0.5844523536536993, 0.5904936242728538, 0.5351366848041528, 0.6368911974676422, 0.4804491634587843, 0.44181421837540136, 0.48032318295495013, 0.42379633524393423, 0.5558320865971264, 0.46339696776395384, 0.42461024828935895, 0.5184874962436096, 0.4791374622592614, 0.6207555934747796], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [3.8618200059768384, 4.58737406770582, 3.8618200059768384, 3.2766957626470146, 6.436366676628063, 3.932034915176417, 3.8618200059768384, 4.58737406770582, 5.792730008965257, 8.519408982882236, 5.792730008965257, 3.932034915176417, 3.218183338314032, 6.553391525294027, 3.8618200059768384, 4.58737406770582, 5.149093341302451, 5.898052372764625, 5.149093341302451, 5.242713220235222], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [0.31413120807264544, 1.5537109874986434, 2.149984739515615, 0.8783970660843665, 0.9867296691717492, 0.8805385758235732, 2.7254234605754055, 2.8413254502762944, 0.3947067828999458, 5.401563807657148, 1.547687493513391, 1.5884299421329062, 0.9091880057157953, 0.9604376513630724, 1.5528246733786015, 0.29677884230190243, 0.9339432621643647, 0.9152575304578358, 2.254384927914003, 1.6062632012785736], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.3786878341513415, 1.0537407600391049, 2.273637578083288, 0.40597904595928264, 0.478437824133481, 0.36720293584658004, 2.8447861380856287, 2.310672905235846, 0.44340820795449076, 2.977356161611031, 1.1055104786089136, 0.44838110197556513, 0.3888785698120411, 0.4481552379755915, 0.4664837053130769, 0.40651591846658247, 0.46207548963572825, 0.44175122718305776, 0.466789160097058, 0.45416309575344654], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}'}</t>
+  </si>
+  <si>
+    <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.6050591781005384, 1.2319737970876001, 0.6947364870418778, 2.5245078344934115, 0.6940985858502591, 1.921664582300038, 1.2499151482274942, 0.5408266683156078, 1.9754336740787968, 1.809926123628488, 1.2949101865812318, 0.6289568380189718, 0.6392249802744533, 0.5498638681852921, 1.196194016243431, 2.6918305284386377, 0.6556115488960418, 0.5943306020717929, 1.2611403028600365, 1.2141405379419319], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.5980612896953622, 0.6175049296758347, 0.6412997478212316, 0.6453802537714955, 0.6260348118832086, 0.6790924760548036, 0.6573193791290942, 0.5411223364484777, 0.7306046238456378, 0.5906546731378158, 0.6587442753344066, 0.5893739319137711, 0.5999898585992879, 0.6181708514236965, 0.6778328008252065, 0.8018805556142918, 0.6779956345327377, 0.6291854230838315, 0.6386883747055502, 0.5853401123630352], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.6305223054601229, 0.5911987008466582, 0.62877383675511, 0.642516369035209, 0.6182374462504397, 0.684362351695599, 0.6463801996794482, 0.5755891215273095, 0.7018762096285002, 0.5834913254345345, 0.6544199185804617, 0.583288462638876, 0.6054092174659339, 0.6286625382038232, 0.7004082791950731, 0.7505817697365346, 0.6501375593356, 0.6154802372936947, 0.6140292064457438, 0.600542403581413], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.2004235215815227, 8.884229915464964, 3.6536058235166777, 2.792070397396038, 2.380970724664281, 0.6680220463915906, 3.1325101502154657, 2.0941094556669615, 3.248886761751654, 1.0112153457258708, 3.411649338622619, 0.3815202509521732, 0.26699402560624985, 1.0891329653214221, 3.474927330291631, 1.6900222461658054, 2.0176057370366567, 1.5251174652888562, 2.0078762632073843, 1.6145695741918609], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4899738953155915, 0.27878204422370556, 1.7834178088426935, 0.5587296160717831, 0.30235984097565566, 0.6011803828564103, 0.5221553854388237, 0.2847420166990177, 0.8112065735353094, 1.7847402932841148, 0.4868283146362215, 0.4515143219147994, 0.33198190217854784, 0.2512338065557157, 0.7942831684465601, 1.8154940303321456, 0.6644542257391622, 0.2917409588750631, 2.873450922160774, 0.4409249646891808], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.49662780151572367, 0.29409454756487535, 0.251693849202729, 0.7346885455183217, 0.3658372986740333, 0.7052947665611977, 1.6678355407264553, 0.3112662379401059, 0.8783940694093371, 0.3898146498796358, 0.5863413747784385, 0.3890390887409703, 0.2938575558947449, 0.24883180608509706, 0.7415753883597357, 0.538114741767272, 0.7370341989756247, 0.29403075841859966, 1.9588290308097653, 0.3337432657128921], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.6080497462833169, 0.4669238320851636, 0.4614723478489479, 0.630841831918187, 0.49054852483418704, 0.5663937628819581, 0.5205187931712182, 0.4551367939877674, 0.633001987413747, 0.4641565723516814, 0.5406487973148723, 0.5440147406963516, 0.49560262472474104, 0.4482804924211553, 0.6279184161294312, 0.5971648194295629, 0.5914328760340103, 0.5185213335388846, 0.42310410223305295, 0.5028461306653633], \'SVC(C=1, random_state=13)\': [0.6557179725030083, 0.5713872985153203, 0.646204104755914, 0.6739564462555552, 0.6790932365761714, 0.6782676498235963, 0.6825113063039885, 0.6162622687943266, 0.737857992572326, 0.6214861311341566, 0.7029434241357928, 0.6588146751738413, 0.6974213351444095, 0.6471831501291069, 0.7386635943471183, 0.7302082915778704, 0.6487316081818317, 0.6398781368706563, 0.6987702661254228, 0.6070938597012484], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.610569640845848, 0.46697048740578095, 0.4642346268989686, 0.6358336224250344, 0.4950517200538323, 0.5693560336144821, 0.5414038983439584, 0.45750918625761755, 0.6521101828944103, 0.4630773951569555, 0.5616689986968664, 0.5213339699271117, 0.49939036248220436, 0.46883194486362934, 0.66735809871395, 0.5974606839381279, 0.5930703225755749, 0.5207695697344478, 0.44269387819168166, 0.5225509672328033], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [5.792730008965258, 5.242713220235222, 5.792730008965258, 7.20873067782343, 5.149093341302451, 5.242713220235222, 3.218183338314032, 3.932034915176417, 7.723640011953677, 3.932034915176417, 4.505456673639644, 8.519408982882236, 4.505456673639644, 7.8640698303528325, 7.08000334429087, 7.20873067782343, 7.723640011953677, 4.58737406770582, 3.8618200059768384, 9.830087287941042], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.7761065990889264, 0.3640752418312204, 1.6107482602511964, 3.5313835574399595, 0.362711078092302, 0.9804124202479467, 1.5745460184558244, 0.9404628824781975, 2.8059990354027065, 0.9499764850920982, 2.834960828839004, 2.2489996777977956, 1.4785589040328933, 0.9825539299871537, 2.19225480405368, 2.856069636025682, 3.424880446616943, 0.4018832698617629, 1.530172685423896, 3.6112826329794583], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.635561599689572, 0.46716192477830604, 0.4643804368192129, 2.4022270931284533, 0.4999373384964442, 1.0995574360940883, 1.0961667617559756, 0.44452929207201153, 1.6607403655420223, 0.42198180387306955, 2.288014698707076, 1.6971989362154263, 0.9830047245777085, 0.4519865294540578, 1.0947088333802522, 1.808933238567794, 3.517384599184733, 0.4933353588808278, 1.6254889186487722, 0.532316814568417]}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.5950533259321455, 0.5942454575644406, 0.6626686791902312, 0.5983836012310513, 1.165153188437105, 1.3823263894955113, 0.5979651005843957, 1.2810620413402913, 1.330866363538508, 0.603469308554735, 1.8151590515273885, 0.5906929256693001, 0.6272749435532458, 0.6558724902036802, 1.9373627076019384, 0.6706847198958825, 0.7183426267260303, 1.295265198263197, 0.6605896448202028, 0.6896989808783283], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.5921370824948001, 0.6183853509946483, 0.5979970036262106, 0.6054870587551767, 0.540743486856442, 0.6645170635663474, 0.5775881461146396, 0.6630521713802927, 0.6402247189133716, 0.6630856105830878, 0.6225306967876686, 0.5849243692111383, 0.6170224003189466, 0.5937986791571179, 0.6706640881539511, 0.6298255680995986, 0.6484165752310472, 0.725662384414053, 0.6228668148191302, 0.6522436051272874], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.5877762881609315, 0.6140588597844965, 0.5772221573212839, 0.6163449353238096, 0.5427190770696756, 0.6469674301059815, 0.5630171655242698, 0.645466836354482, 0.651243214024155, 0.643766778888039, 0.6087676863995986, 0.5975362872545673, 0.5931961937575332, 0.6053090990573025, 0.6297023419931972, 0.6228247844566237, 0.6407798180656694, 0.6976641388063276, 0.6307182913078441, 0.6130637424899721], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.564168969802726, 3.604510501922391, 0.2331064617261807, 10.38974982835143, 0.16849146577092516, 6.21979984044454, 0.28880261455801953, 2.667884687224297, 1.0392899851446196, 7.459610007587962, 1.7706131084509273, 8.879344486135743, 0.411903269515227, 8.911974778087554, 1.4202916188926693, 0.3608452720588002, 0.4509469484909731, 6.217388405532686, 1.2202214527940263, 3.0782033501820614], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4830698328723697, 0.2640697497509802, 0.23683176595074545, 0.42936048286065315, 1.8784455127194437, 0.3950667843856559, 1.7826410476667245, 1.199138287582268, 0.20901005684172366, 0.448367257259174, 1.4909110053321055, 0.35736422709731397, 0.5611554833026547, 0.24915837102651994, 0.2910526270437673, 0.3688627400865086, 0.4289819890456132, 0.453384722366699, 0.36464372141467255, 0.3669352179613977], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.7002873052046285, 0.30026012796912727, 1.5292001514949511, 0.5393317183391716, 0.27836070440199384, 0.4944599209041011, 0.8569699235692586, 1.4857576076760932, 0.2063152249097015, 0.5014421810088912, 0.42847163764455354, 0.37702640876089805, 0.4358111541570238, 0.23185883022012002, 2.3318561888236866, 0.31151259796738756, 0.4389144635636851, 0.5975476297731271, 0.44374575426963647, 0.4086946051030441], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.5768158311410201, 0.4778035378942525, 0.46380209936431605, 0.5226564025348023, 0.4348816054456274, 0.5258952923787116, 0.4361575968461539, 0.5814404856622875, 0.4476128864998127, 0.498901361752195, 0.5440522013062588, 0.4908260298750802, 0.49748662371777236, 0.54358939541349, 0.49341860726371617, 0.4503964756517568, 0.5609088612581589, 0.49456296688604706, 0.5625881687504131, 0.48130184871522286], \'SVC(C=1, random_state=13)\': [0.6385227066700983, 0.7297906968737603, 0.6074107758043564, 0.648105769471157, 0.6372770337889669, 0.6505212433459776, 0.5935924669400107, 0.7080822572851815, 0.6411198538119225, 0.6840889324110926, 0.6742416349798567, 0.6325196192253189, 0.5429719606681662, 0.7021731457542909, 0.5790722379881521, 0.6829550599817785, 0.7186811172721589, 0.665755411565831, 0.6785340638940959, 0.6319780555542794], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.5780625536435041, 0.4821035266408717, 0.46610709512309534, 0.5402334906864729, 0.4354132675441556, 0.5277645206379041, 0.4029642424834145, 0.606215429222748, 0.4670187530506766, 0.49887480768084314, 0.5481516773557489, 0.49109894363026135, 0.4811562214972973, 0.5265211924791717, 0.49302098134988565, 0.47210648252888326, 0.6008981031765923, 0.49531321303580766, 0.5645272080150335, 0.48176196471833865], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [6.4363666766280625, 4.58737406770582, 5.792730008965257, 5.898052372764625, 2.5745466706512263, 6.553391525294027, 1.9309100029884194, 5.898052372764625, 7.08000334429087, 5.242713220235222, 6.4363666766280625, 5.898052372764625, 3.218183338314032, 6.553391525294028, 4.505456673639644, 3.276695762647014, 6.4363666766280625, 5.242713220235222, 5.792730008965257, 4.58737406770582], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.8627499966589194, 0.9825539299871541, 0.34402364438642524, 1.5979435447468069, 0.9082573628383129, 1.6336100630381423, 1.544653582142045, 1.6409821559128361, 0.9650083240945262, 0.973040327373253, 2.1747399959641847, 0.37976699123768126, 0.8636420470674853, 1.6400345922557635, 0.8627114041900027, 0.3398174534679318, 0.9360465306582285, 2.9454823141790816, 2.1955306981639255, 1.0225034677569032], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.663774276913369, 0.468766562010213, 0.3684134744209207, 0.46685091627097985, 0.36356159731505205, 1.0739208744988662, 0.4034430905999109, 1.7228560162357351, 1.1034072101150498, 0.37702754696780694, 2.245946312858632, 0.4326688341440172, 0.3429292537844896, 0.4623625512176794, 0.3368412790171575, 0.44292465484010446, 0.4520028085949282, 1.1234486409647817, 1.7020596351779655, 1.069206645445592]}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.2674258742177926, 1.9564515808771146, 0.5955010694598618, 0.7469544316712521, 0.6605302548743175, 1.3030843875308467, 1.2042470528600882, 0.5719767289488243, 0.6192375100615032, 1.9536412670641605, 1.2290576171553464, 2.4814087535642986, 1.3032046066092842, 0.7151747798436521, 1.2972819626371237, 1.2688342614610695, 1.8528819684716946, 1.860704149620439, 0.7585336568940665, 1.993142494694512], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.6494811043969752, 0.6667103115085131, 0.5940087876485582, 0.7239109522784581, 0.5847551421969731, 0.6166508709549104, 0.6842009608878762, 0.6117758983155395, 0.6010851992911883, 0.7054568526639422, 0.597289689287295, 0.6181822290756517, 0.6007357407815466, 0.6746093112463601, 0.7376272241432564, 0.6182145927920091, 0.6564942980249838, 0.6240013862596683, 0.7006884790934417, 0.6852324714758816], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.6315882093278837, 0.6426231847033248, 0.6038988120097171, 0.6948649235359856, 0.5697486606379728, 0.5988991526055285, 0.7064417134754256, 0.6079920067342539, 0.6102260955590043, 0.6712653085931691, 0.6155371387419433, 0.5971043227939518, 0.6129644410684844, 0.672817064174635, 0.703107825957672, 0.6154047314290095, 0.6291677487701456, 0.6027848962480785, 0.6496961324348683, 0.6952499968479126], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [0.4174245992679203, 1.1230936809507073, 0.394029634369545, 3.4819597627093652, 3.171915410801443, 4.462591654903584, 0.5980167489308397, 2.223071382816178, 0.1908137670729019, 2.278656967877158, 0.4815980282152026, 5.093384243196218, 0.3676289333431102, 1.4000297051262398, 1.8164587845009372, 5.647375898164342, 0.47415182299907094, 2.314407295293441, 0.3427611466909405, 2.5094846478301633], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.38208077686182135, 0.5317196152223668, 0.32492916186580506, 0.49979743344273686, 0.23890220375168106, 0.35458051844889366, 0.7282866726385283, 0.5850500844060531, 0.18121868133091676, 0.553883923899072, 0.41395599574032227, 0.3357861241331943, 0.47074145793020694, 0.24890877687257693, 0.60910160609313, 0.3146261674120212, 0.5728258351097999, 0.34112494011866573, 0.3169549473740842, 0.593207974328024], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.38579768780608487, 0.5549572030159454, 0.4737755050991997, 0.5397386630370116, 0.3116347479842399, 0.43539828845091494, 0.7283676170345286, 0.5666351371032301, 0.18100382170302032, 0.3812875989353428, 0.47584356045422893, 0.37658774664647837, 0.44183476185689957, 0.28846830471388296, 0.7056898702052555, 0.39548424132154103, 0.5098528634832872, 0.40507355012922935, 0.30475320395786654, 0.5576581826743052], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.47908147748886926, 0.6495672655740791, 0.5179911815605305, 0.5879727992476373, 0.45000827279812255, 0.4630884519974514, 0.6529136529976848, 0.5779221056766536, 0.38496069698761687, 0.48237385522747767, 0.4773599805538611, 0.4797533125523394, 0.47809438906175084, 0.43105429389158406, 0.5426073426842244, 0.5420485752022142, 0.5958937779699306, 0.55364477660307, 0.4800307030424982, 0.5481158338868095], \'SVC(C=1, random_state=13)\': [0.5655754183885972, 0.6947953385759853, 0.6043059530096981, 0.7326382579001808, 0.5658822467351343, 0.7049963334068812, 0.7093102788819845, 0.6640525251170637, 0.5516355436885909, 0.6933465042604865, 0.5868001134946425, 0.6667071426985952, 0.5501761457856313, 0.7464222885121684, 0.6409958718283691, 0.7362217854960809, 0.6346331058834959, 0.6929401318642213, 0.6300499502088116, 0.7322852508964433], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.47955953058573464, 0.6538886118131105, 0.539563159977188, 0.5863833221322952, 0.45311221052689854, 0.5017253718349886, 0.6953378630185296, 0.5605196563321964, 0.3856074027424455, 0.4851705347605142, 0.49676288000051366, 0.4810544413186649, 0.5165955169493973, 0.4503768120134966, 0.5207313715837641, 0.5273291321486092, 0.5961892734602369, 0.5548801578823761, 0.5234587722035183, 0.6046464592041947], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [5.792730008965257, 5.898052372764625, 5.792730008965257, 5.242713220235222, 8.367276679616483, 5.898052372764625, 7.723640011953676, 5.242713220235222, 4.505456673639644, 3.2766957626470146, 3.8618200059768384, 4.58737406770582, 6.4363666766280625, 5.242713220235222, 5.792730008965257, 4.58737406770582, 3.8618200059768384, 3.932034915176417, 5.149093341302451, 3.932034915176417], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [1.5332065967952424, 3.477637397577896, 0.9257721709278081, 2.1669590925190896, 1.581786466814899, 2.233307928391335, 2.7761065990889264, 2.1890753711431716, 0.8823294807733617, 0.327214777457751, 0.8699518525490769, 1.6357515727773495, 1.5425503136481808, 1.0802862646723206, 0.9804198636901571, 1.5831993589974191, 2.8059990354027065, 1.5789163395190051, 1.5796831983210349, 2.239486075183895], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.0040807295367908, 2.973093660557704, 0.47568921552147636, 1.0274821814292308, 1.041415292899266, 0.4797646007884867, 2.314006052817109, 2.3299259744636216, 0.39316873086949017, 0.4493286656326382, 0.3400970211027638, 1.1252996606217496, 0.4609230160439859, 1.1264730882787963, 0.4636514726313513, 1.091754133644534, 1.6708130465828224, 1.0434849393430177, 1.0447748110792325, 1.6711662216055256]}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.7565726771439378, 1.2875546145007268, 1.2284357858891704, 0.6133502331198636, 0.700752358765207, 0.6812831877989284, 0.794862117507731, 1.3198252072076382, 0.6149727752002893, 0.5867284888779434, 1.3371411391424173, 0.5498075547413905, 1.2300711588306787, 0.6078367340818689, 0.6353866448439172, 1.1744202820327059, 1.8461560925127436, 0.5021802856552459, 1.2410117359757504, 1.2242268080819472], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.6593371137966366, 0.6992447047035061, 0.686294609882622, 0.6607216942003079, 0.6491685727203961, 0.5975821535493266, 0.634813610986744, 0.6660131776665484, 0.6180016651262995, 0.5902515011656666, 0.6064838381936904, 0.6088817930371289, 0.6298397883907668, 0.6318664618527489, 0.6421268652467467, 0.6052914041614385, 0.6123509335645485, 0.5414679589312772, 0.6056073919771535, 0.6248476196920552], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.6492590768512494, 0.6697468481584005, 0.6874974638655197, 0.6525172162168488, 0.6280730388702789, 0.5891755176292504, 0.6538427784697965, 0.6428097486862336, 0.580240993437286, 0.5823471158293849, 0.6094038336102535, 0.5922630395900844, 0.6107596916221956, 0.603249297322292, 0.6201258868551653, 0.5694467090553944, 0.6376035726017248, 0.533881179242668, 0.6177144665850905, 0.6081960998199265], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.1877351493210244, 3.0358890442157707, 0.5999429027072026, 2.9828876288695514, 2.1174577937275485, 1.6687151958297939, 5.969142171485283, 7.502268123087099, 4.835690271811283, 1.8022389509084948, 8.430465254469516, 6.538055997664123, 3.6376796871910315, 4.679339674444174, 3.7585936647555656, 1.091933957837066, 5.5429453286275026, 1.7818673163579724, 5.428855078648213, 1.8746458069173637], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.36803466555728875, 0.41889126097290247, 0.5748479015051586, 0.6099137168730207, 0.383668620499972, 0.2777354517697968, 0.4285353397300432, 0.6245633328219878, 0.3770015963123803, 0.23319379839692667, 0.3295755220310029, 0.38484142954962225, 2.1818352519493276, 0.2942473796480529, 0.40283695078007087, 0.2985544564742283, 0.37378766114529915, 0.21495747404746385, 0.2721285669833187, 0.33654366159740223], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.0525055106434333, 0.3979237422081987, 0.7189357418887311, 0.5538753033645574, 0.511539827379849, 0.27641913148879177, 0.34632377990580165, 0.8162506609071652, 0.3449822251946321, 0.30280052435172405, 0.21425850708318725, 0.43979317274589075, 0.3230197168815934, 0.3130497412046773, 0.4038448649872238, 0.41474465562464574, 0.5763971536143541, 0.23495682403096085, 0.3147942018741971, 0.3876186389191358], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.4661669440771566, 0.5591859310231162, 0.5026084135423063, 0.6033369552936604, 0.4961792450995236, 0.4845009495746922, 0.46151793479306896, 0.6548261106989484, 0.4977680643306431, 0.4957880421416259, 0.47824717648554105, 0.5265993135327358, 0.4986522692516981, 0.4270880876636148, 0.4639531251756364, 0.461810040625106, 0.5193304958876189, 0.4435839274364308, 0.46421483135252845, 0.5036148442056072], \'SVC(C=1, random_state=13)\': [0.6442707493116266, 0.5702535759099725, 0.6899989480976931, 0.611231385614008, 0.6627435970572392, 0.558934468059458, 0.6636319621559288, 0.6490204749220088, 0.5763138980738028, 0.6069093152964934, 0.6011604767037816, 0.5729020376630275, 0.6364593001412865, 0.6268867480242885, 0.7221863141381267, 0.5652923979961276, 0.700823313448691, 0.5706495062610117, 0.6316992953328933, 0.5538485382798997], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.49448359369692285, 0.5810347183433995, 0.5392811129962735, 0.624693438840617, 0.5148486337968349, 0.4840725366924367, 0.46222739582031386, 0.6569065017205932, 0.4807102609238515, 0.5185415943933723, 0.46085974982762895, 0.5675046102660373, 0.5173108254361839, 0.4667295562955305, 0.4811292688707969, 0.4961744380095281, 0.5188093717344624, 0.4432677950353461, 0.46448519784507475, 0.5061927268038737], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [7.723640011953676, 4.58737406770582, 5.149093341302451, 7.8640698303528325, 3.218183338314032, 6.553391525294027, 3.2181833383140317, 11.140765592999847, 2.574546670651226, 5.898052372764625, 5.792730008965257, 3.276695762647014, 5.792730008965257, 6.553391525294027, 5.149093341302451, 4.58737406770582, 5.149093341302451, 5.898052372764625, 3.8618200059768384, 5.898052372764625], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [1.6717057584951376, 1.597943544746807, 1.5507214048847378, 2.9454823141790825, 1.476455635539029, 1.7021004086495943, 0.9330126192868823, 4.224530737999904, 1.4722490985513015, 0.9373738090819175, 1.5745460184558244, 1.0194143943606233, 1.5507214048847373, 1.0046702086112353, 0.9360465306582286, 2.240680021266029, 1.59719800641053, 0.9121684570615558, 0.8989136459853745, 2.25637177067249], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.4757093675461156, 0.43812528127947786, 1.0425879185156475, 1.124416723046942, 1.6007135101755636, 1.1577363860241838, 0.44896889722358185, 3.6812755169492757, 0.36117302606184637, 0.44815523797559137, 0.4024922956977893, 0.4603061859858247, 1.0700372010014039, 0.4547645943430116, 1.000096023263323, 0.476449663392233, 1.122498001200168, 0.42818046909071666, 0.44150661815024755, 0.49088284063429466]}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.225619156332359, 1.3227652484729333, 1.8798868642570599, 0.5507433878995505, 1.8480260092666294, 0.6519396921119561, 1.1631253798145695, 1.9038100662706507, 0.5763232974776973, 1.3453978811792273, 1.2677948010468558, 0.5768117692940006, 1.2234416200395664, 0.5330028474409665, 1.2512415836133293, 0.5638658358524934, 0.6477527520424836, 1.3033912397189908, 0.6277260439082873, 0.7713646700260753], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.6367434368248625, 0.6276095147871399, 0.685007830702811, 0.5882959577351276, 0.58324671297026, 0.5929195193282563, 0.5841414349053838, 0.684119786980081, 0.5966850763428484, 0.7165235092920318, 0.6607379270908326, 0.5911145965596347, 0.5860653891404422, 0.6019478769611167, 0.6289448650026677, 0.631532646567673, 0.5673198429106326, 0.6025954134496764, 0.6066098546514668, 0.6695080255415949], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.5973675922890267, 0.602043745742848, 0.69738224264057, 0.5740404717718165, 0.5898469780212967, 0.5965723550369632, 0.5989938341177089, 0.6691377710238521, 0.5726822275134041, 0.6940490004790972, 0.6356927955088089, 0.5563705243095141, 0.5933121901677376, 0.5943214169194879, 0.645855100667117, 0.5965466937245523, 0.58427630872195, 0.5909032531963722, 0.6111942679750072, 0.6614335108163332], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.1864235140820316, 2.2236396213489056, 2.078355172626382, 0.26113032846161505, 1.700250244939967, 2.897660546819197, 2.1870899671650403, 1.544585566871323, 0.23739275949310773, 4.464295129063591, 3.841789015322913, 0.13950099461508747, 5.958472826588951, 1.159693515247938, 3.476192208450782, 0.20685189232306228, 2.260152217691126, 0.2159977659904755, 2.086562952001466, 0.7774922926321765], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.30418774253813063, 0.2003702783028071, 0.7894832783673035, 0.2373013866204567, 0.18662081516521414, 0.38377645840435365, 0.6668321179252562, 0.5178543761893151, 0.203006392088793, 0.6675461342297468, 0.43130768529330954, 0.14039221217202097, 0.3693715330094986, 0.18837497527148056, 0.467528281601183, 0.21508863112041424, 0.2638301122282587, 0.25631173990686523, 0.3724141720423919, 0.7173181940969249], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.3918243882887987, 0.1747053057879002, 0.8094979594534405, 0.27075075008328237, 0.2654243049447243, 0.3937498048190377, 0.6776783979060441, 0.5017816249953282, 0.21664354032862457, 0.6284171113852757, 0.5081438070545802, 0.11984293605235494, 0.37472379579431825, 0.19614561674485997, 0.5557188907611905, 0.23672081902050926, 0.22878916363761403, 0.22141392127691462, 0.21135758164667084, 0.7135710459373474], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.46676837233366114, 0.4445532416338193, 0.5673202306589488, 0.4261525072388276, 0.4608023079709996, 0.4777843868028735, 0.5636163902220382, 0.5897617431415291, 0.42706112854943507, 0.6360205147205775, 0.49860903776273396, 0.42032581224615534, 0.47979559034148883, 0.44108642447776075, 0.5284627720228928, 0.4431764715652437, 0.4244009171940196, 0.49901708713716486, 0.4775173423181017, 0.5832511529571291], \'SVC(C=1, random_state=13)\': [0.6772853526377779, 0.533880960757025, 0.6308896574283039, 0.6060855576389061, 0.6643663434078683, 0.5685441538058696, 0.6803286263320947, 0.6754991227862408, 0.643644389139393, 0.6280771837923425, 0.6779355744811918, 0.6441307107032466, 0.6635625907246571, 0.5045327188174663, 0.6572819766655922, 0.5243006317854162, 0.6044636427059051, 0.5997911227443139, 0.6157584687049502, 0.6051276774253985], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.4331499086854627, 0.44717810024030263, 0.5554926347906591, 0.46268894206174715, 0.4748645192173798, 0.47934364595517037, 0.5844523536536993, 0.5904936242728538, 0.5351366848041528, 0.6368911974676422, 0.4804491634587843, 0.44181421837540136, 0.48032318295495013, 0.42379633524393423, 0.5558320865971264, 0.46339696776395384, 0.42461024828935895, 0.5184874962436096, 0.4791374622592614, 0.6207555934747796], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [3.8618200059768384, 4.58737406770582, 3.8618200059768384, 3.2766957626470146, 6.436366676628063, 3.932034915176417, 3.8618200059768384, 4.58737406770582, 5.792730008965257, 8.519408982882236, 5.792730008965257, 3.932034915176417, 3.218183338314032, 6.553391525294027, 3.8618200059768384, 4.58737406770582, 5.149093341302451, 5.898052372764625, 5.149093341302451, 5.242713220235222], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [0.31413120807264544, 1.5537109874986434, 2.149984739515615, 0.8783970660843665, 0.9867296691717492, 0.8805385758235732, 2.7254234605754055, 2.8413254502762944, 0.3947067828999458, 5.401563807657148, 1.547687493513391, 1.5884299421329062, 0.9091880057157953, 0.9604376513630724, 1.5528246733786015, 0.29677884230190243, 0.9339432621643647, 0.9152575304578358, 2.254384927914003, 1.6062632012785736], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.3786878341513415, 1.0537407600391049, 2.273637578083288, 0.40597904595928264, 0.478437824133481, 0.36720293584658004, 2.8447861380856287, 2.310672905235846, 0.44340820795449076, 2.977356161611031, 1.1055104786089136, 0.44838110197556513, 0.3888785698120411, 0.4481552379755915, 0.4664837053130769, 0.40651591846658247, 0.46207548963572825, 0.44175122718305776, 0.466789160097058, 0.45416309575344654]}'}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82c547250&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb83958e210&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb83958cf90&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb83958fa50&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb83940d9d0&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f885110&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f885190&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f886e50&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f887890&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f890950&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f891850&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82c50d890&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd3853650&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd2e56950&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd3d9550&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd59d910&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2233950&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2dc4550&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd38ba510&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd21f55d0&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd3898650&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd21f50d0&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd3898310&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd5a7110&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac19cd0&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f04900950&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0ef959f650&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f0478d490&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f049148d0&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f04926d90&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef959c510&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f0492c2d0&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f0492f310&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f049030d0&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efa163250&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0ef95b1d50&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bc34890&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b8176f050&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b81782550&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b5e5190&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b5bcd50&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b5bc750&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b5bcb90&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b5bd790&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b5bccd0&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bc1b350&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b5bfc50&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b5bc510&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f925068f910&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9244b602d0&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9245613650&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455d8210&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9250677950&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9250811b90&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9245590890&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9245592e90&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7f925082e0d0&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f925082c990&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f925082ef90&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9244b69010&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb83959c790&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f8d5210&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb839409990&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f8cc190&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c559d90&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f2033d0&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f201950&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f2012d0&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f202cd0&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f202790&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f201210&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f202d90&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9250657910&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92456009d0&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9250663650&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9245635bd0&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9244b50890&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455f95d0&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9245620d10&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455c7890&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455c6f90&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9250671c10&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455c4a50&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455f3750&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd57e9d0&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd551d90&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd2e0eed0&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd21ff110&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2e0dad0&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2e0ce10&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e0ec50&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e0db50&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e0dd10&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd2dcd0d0&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd2e0d8d0&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd2e0fa50&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bbefe90&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b5d0550&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b592ed0&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbdd190&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbfb910&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bbf8e90&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bbf8e50&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bbfb550&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bbfb410&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bbf9b50&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bbfbe50&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bbf91d0&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac4c9d0&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efa149cd0&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efa11d790&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef95a5490&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efa16a4d0&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef95c3a10&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef95a5610&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f048f3890&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f048f0590&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efabcb0d0&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f048f0510&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f048f1f90&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
     <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f8b3950&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb839597710&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82c51f810&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb8395bf790&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb83959f8d0&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f248e50&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f249850&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f249450&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f24a250&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f24b5d0&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f24b990&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f248590&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f0493d790&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f0491d250&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f04920690&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f0491c190&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef95d2190&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f048fd690&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efa114510&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0f048fc210&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efb4fbf90&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f049330d0&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0f049221d0&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efac30e50&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bbf78d0&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b7ca0d0&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bc60950&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7b5d5190&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bc2aed0&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7817ba50&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b595e10&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b5d9550&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7b5d82d0&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b5da4d0&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b502b50&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7b5d8450&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd389ed90&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd38b3cd0&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdebc7f90&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd55b690&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2e2f510&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd2e2f650&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e2f710&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e2f6d0&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e2f350&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd38c50d0&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd2e2f290&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd2e2f150&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9244b0c310&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92455b39d0&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92507f7c90&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455b2dd0&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9250815bd0&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92507ea6d0&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9244b51490&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9243f7c950&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9250652810&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9243f99c10&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9243f7ca50&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9250653090&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f047706d0&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac09fd0&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0ef95c8bd0&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efa189950&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef95c9310&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0ef95cabd0&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef95cab10&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef95cadd0&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0ef95c8150&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0ef95c8050&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0ef95ca850&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0ef95cacd0&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9243f44950&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92455c5c90&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92508318d0&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9244b55510&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9250832110&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9250830390&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9250832cd0&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9250831050&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9250831e10&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9250831590&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9250831950&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9250832150&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd583650&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd5bd5d0&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd2214750&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd5bd910&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd222fe10&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd38b1490&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e42510&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd38b0250&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd38b0dd0&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd389d0d0&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd38b2990&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd38b1110&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb83940c650&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82c54a890&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f256cd0&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f254190&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f217a90&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82f217c10&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f217f90&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f216a50&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82f215750&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f217750&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f217790&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82f217990&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bbc5690&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b81947650&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b5f0990&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b82f6d150&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bc07e50&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b7bc06310&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bc05d10&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bc04b10&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b7bc062d0&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bc06050&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bc06850&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b7bc06f50&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0f04913650&gt;: [0.689092806961391, 0.6907564807292882, 1.3866091995895329, 0.6214351943759663, 1.3329459086719269, 0.6580794523787667, 1.3234650806777284, 1.387195205977111, 0.7589792741544237, 0.6879187766415465, 0.6547968383995523, 1.3659243787376272, 0.546474830355464, 0.7192932215707828, 1.3031876594734682, 0.6315171435488727, 1.3787529197784405, 0.5814692215381322, 0.6191210124079748, 1.4032607914791317], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0ef95c9cd0&gt;: [0.6089729855762509, 0.6821723820775059, 0.6774616207497334, 0.6066865445801285, 0.6483490736763716, 0.6439966611188063, 0.6816786292726479, 0.6827272694250197, 0.7178950745117022, 0.6298516524854355, 0.6068470742541704, 0.6216579844367401, 0.6456310522587511, 0.6430288658335577, 0.7601998373744385, 0.6756045742352139, 0.6881022453807778, 0.5934433949519595, 0.6355093633942743, 0.5800170132817082], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0efac20490&gt;: [0.6223881762961612, 0.6948242115600259, 0.6823340149221149, 0.5882912569541808, 0.6398622759030793, 0.6592220909022877, 0.6668855271935119, 0.6629121293334095, 0.6740334845691821, 0.6219188337036311, 0.6079822947492309, 0.6191635584669649, 0.6356837838537595, 0.6300343842688921, 0.6648611251795365, 0.6632601081592356, 0.6537326063316733, 0.586598780974412, 0.655496009561338, 0.5802369008277228], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0f04945690&gt;: [3.6291988574977005, 2.617536135194733, 2.4603427760895387, 1.6115573147173163, 1.131884232819152, 2.7610813405034524, 2.658882379043039, 1.9019797312539528, 1.7082583587729687, 7.877944720666277, 2.714599238612737, 2.742400248720251, 1.2581365469152666, 1.748551664021704, 0.5653397024244718, 3.877585656596693, 2.96178199497366, 4.32498806650851, 1.9799818520361432, 1.6233317129031086], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efac0e810&gt;: [0.21201571687309326, 0.5936976500358798, 0.47603665039779436, 0.3589540930227657, 0.3013849467384595, 0.2909409877353683, 0.3910166888061631, 1.9962711400269808, 0.3742262136728802, 0.479899866388453, 2.491947334000244, 0.3858324496942044, 2.1227900555192547, 1.3893059347766261, 0.8237824125402397, 0.5295667567091097, 0.48553341139280165, 0.48506784061523806, 0.49466307987440866, 1.4618534247101147], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0efac0ec50&gt;: [0.19161523044183137, 0.6732930963171653, 0.44421972042573676, 0.30052465094092756, 0.3799961684376027, 0.28961307892450133, 0.41099442210932857, 0.5121720319121297, 0.4386136311567997, 0.5008099851326764, 0.1545565061791383, 0.5930594016379453, 0.3387805103374914, 0.6452457758442354, 0.5282426353181349, 0.5610084781418492, 0.4665386463994877, 0.4898800415984105, 0.5479587394496653, 0.5348330910925198], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efac0c950&gt;: [0.44903706950452454, 0.6167683100177437, 0.5579547075890875, 0.4564085019331785, 0.49933053832654645, 0.43606333819461834, 0.5153763798725587, 0.5767812402786802, 0.5324612043518255, 0.5236914798538475, 0.42714342395523, 0.5252878984693592, 0.5161694066763437, 0.5830235291700668, 0.528951442629366, 0.49780431655658836, 0.6278997270157398, 0.5365942624321116, 0.553138035155851, 0.4557966651216528], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efac0cb10&gt;: [0.6590600719031212, 0.6999723342781049, 0.7401541648224971, 0.576630979589728, 0.6370177230374622, 0.6493868518881798, 0.6126759013686234, 0.7367699631534629, 0.6783354343534456, 0.6880734120556492, 0.6505025236229808, 0.6168537196532072, 0.6537030164992029, 0.6186566050334197, 0.7165272927664903, 0.7224664148904621, 0.6828006018921643, 0.6648025482499867, 0.6788462165017854, 0.6577372988209508], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0efac0c550&gt;: [0.5146101578327347, 0.6388705411228387, 0.5405154733837156, 0.48065246338702233, 0.5213007254417539, 0.4368875777755483, 0.5181822151164261, 0.639056413314459, 0.5754356239780769, 0.544526934025305, 0.4491894199251205, 0.5277701523987814, 0.47912469391424267, 0.5847407933850941, 0.5531348733716962, 0.4769690952600676, 0.5866828739806038, 0.5403513495530223, 0.5815953838902054, 0.45741745102089243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efa183110&gt;: [4.325238406694059, 5.149093341302451, 3.604365338911716, 12.504940971734522, 5.7669845422587445, 4.413508578259244, 5.7669845422587445, 8.09143239347528, 5.7669845422587445, 5.149093341302451, 4.325238406694059, 12.504940971734522, 5.046111474476402, 5.149093341302451, 5.7669845422587445, 3.6779238152160367, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.8846781043456575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0ef95b0850&gt;: [1.048372114337216, 2.5633576486482292, 2.399873606095325, 2.5657613840697877, 0.3055268007815108, 1.1618538348406044, 0.3356083487170362, 3.970732525158951, 3.800030910826415, 0.39663720658031043, 0.26158230923478637, 1.1877418210745538, 1.0345091707260172, 2.4240262240906487, 2.454283060517341, 1.780527832278642, 2.347819812386438, 1.0804459971556193, 2.464748023392632, 1.0732347908909428], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0efa1142d0&gt;: [0.4212067240459406, 2.6098129497201006, 2.5050174777939733, 1.248922564086867, 0.39006028582003893, 1.2334595905828363, 0.5156432182112342, 2.6294807820692596, 3.193453336927663, 0.4954941230033722, 0.3581199779713281, 1.2580534950258104, 1.1559201651718867, 1.7911771760192408, 1.8755250327990742, 1.148742376067214, 1.7969424633324527, 1.1854044662127736, 1.1574593859946092, 1.1752099434138505]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9250691890&gt;: [0.748665343074412, 1.333427798236991, 0.7064511499131898, 1.3889561513183377, 1.2577801305622045, 0.6131387277344642, 1.48796164409893, 1.991582928883432, 2.03564795325867, 1.2875945990701454, 0.8112860902143825, 0.6541050834646338, 0.607800235121583, 0.5679128058218329, 1.382873681446666, 0.6371516886962942, 1.3503745280097215, 0.6163610358300164, 0.7026407834332269, 0.6175385636844694], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9250683650&gt;: [0.7089325158944532, 0.6141752895665615, 0.6897089143753921, 0.6347150625897301, 0.6598185657683194, 0.6166263712950322, 0.7300640953598537, 0.6348810617612026, 0.6985109195938749, 0.7401663761780496, 0.6122597353198944, 0.6275354175180134, 0.6363372370507282, 0.5981774331331161, 0.7185047381407107, 0.5875042814600073, 0.658657785030079, 0.6029359797234776, 0.6611267801614954, 0.6197298162943629], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f92455de9d0&gt;: [0.6987081374765388, 0.6235128170497862, 0.6675555505476383, 0.6198466181682846, 0.660161699186013, 0.6299567651372846, 0.702025594217861, 0.6546604284611132, 0.6825936697463553, 0.7371934889142083, 0.6181813088043561, 0.6405224829982119, 0.6280345353386487, 0.5992107445591965, 0.7067224663897346, 0.5849421953566851, 0.6478053672255555, 0.6144533686181878, 0.6750959485790189, 0.6277171210205679], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9243fc2310&gt;: [3.7847698934102203, 2.635659319622094, 0.25907353948984874, 3.350248398226686, 3.892004669684663, 0.29965640767873475, 4.699975596333572, 1.399624725839616, 6.469166773718593, 2.1916185256609184, 0.21217323264837734, 3.641031238868882, 1.9856709639142922, 2.0079065056229792, 0.818048841059957, 7.84345776215778, 1.1456322308344349, 1.9718333450144732, 1.9502101690075626, 8.100309963930195], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455dc8d0&gt;: [2.8211589213748307, 0.4766660635994175, 0.2515807053844405, 0.5538478249964033, 0.5363070057194055, 0.409394048568714, 0.6167423310683957, 0.30539897986118686, 0.41792479469038013, 0.7522880819497638, 0.26798098356039224, 0.5314162984842896, 0.39122740842245995, 0.4209553148396918, 0.5642409728701124, 0.22869387423940907, 0.43761249713205613, 0.31423248405183296, 0.4672202324532389, 0.3399622153041623], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f92455dd9d0&gt;: [0.46132817115048375, 0.5194312971138606, 0.3439006245395646, 0.7921294013301561, 0.4044031466982122, 0.26483447537485283, 0.746846199244099, 0.12547048369906574, 0.5142348416336976, 0.574097258790142, 0.281358816362671, 0.6015574871537471, 0.3056000447432851, 0.3931024363276984, 0.5768334184306086, 0.3203086043727148, 2.5478934692982813, 0.24812861285236817, 0.7130347372305473, 0.21770284132448847], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455dc690&gt;: [0.5425311687368678, 0.5447279741649356, 0.474560247754323, 0.5753571176869977, 0.5340599780205804, 0.5209929815603956, 0.6365687490204126, 0.5035892259732263, 0.5408759945526834, 0.6209762921715456, 0.45297106184970476, 0.5726522901536669, 0.4644356291546503, 0.5199190625931288, 0.6550300770248494, 0.41071964904880365, 0.539437625231389, 0.4812669604200264, 0.5844129332307869, 0.458950271264212], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455dd8d0&gt;: [0.6576565260466851, 0.6834112524370223, 0.6321088097700259, 0.6407248796134253, 0.6937301531044947, 0.6101905895940078, 0.6730478972933875, 0.7496062965727092, 0.6988172355965548, 0.6744569967555147, 0.7038563220089448, 0.6873272969677388, 0.6213214644286186, 0.6012516412034937, 0.7379850566217983, 0.6736886336657297, 0.6134778330983677, 0.7511975019137112, 0.6794125357186247, 0.6519030825637127], &lt;method-wrapper \'__str__\' of SVC object at 0x7f92455df5d0&gt;: [0.5636288094811338, 0.5270547499167062, 0.47742047644693186, 0.577479093530818, 0.5779045905426365, 0.5020557362566855, 0.6517708550401676, 0.5045224913764652, 0.541518334428559, 0.6238021888836708, 0.4530966338819992, 0.6040565124641886, 0.4662127826765047, 0.52344595225146, 0.678937169074502, 0.4309634440174387, 0.5628324020379771, 0.5037264196200559, 0.6281121225123154, 0.48322330341390823], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9244b71c10&gt;: [7.929603745605774, 3.6779238152160367, 5.046111474476402, 6.620262867388865, 5.7669845422587445, 5.8846781043456575, 6.487857610041087, 5.8846781043456575, 5.046111474476402, 5.8846781043456575, 5.7669845422587445, 5.8846781043456575, 5.7669845422587445, 4.413508578259244, 8.650476813388117, 3.6779238152160367, 7.20873067782343, 6.620262867388865, 4.325238406694059, 11.769356208691315], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455de090&gt;: [1.7415192948971614, 3.2399552329588612, 1.7577378992214876, 3.9093416110048165, 1.0923166058839404, 1.0142476121583681, 3.098774428104306, 1.8408551545727958, 1.0622350579484148, 3.2541010937866153, 0.3298547072680006, 3.8917284228955245, 0.9929203398924205, 2.394670910575161, 3.9203571025685164, 0.262113252865848, 1.7171913884106715, 1.797077428527955, 3.0930207866552712, 1.8018848993710725], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f92455dd190&gt;: [1.1548778451491062, 1.9151181665528831, 1.200455216476641, 3.278158766791378, 1.212933730707001, 1.192918701888539, 2.536957785642684, 1.236949948749677, 0.4717212969321058, 2.6931405120793523, 0.42227161433631694, 3.2781357359060768, 1.1635551368017039, 1.1707515637524255, 2.615198245751247, 0.3966080167746938, 1.1531127441940086, 0.5328937447125214, 2.5149855398693215, 1.2110619625157277]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7bc48550&gt;: [0.6469405585884602, 0.6484051380989727, 0.6869190799088427, 1.3438698142275305, 0.9003600935281864, 1.299006827805864, 0.6738583375181573, 0.6044516294604708, 1.4414975564949943, 1.410702487674803, 0.6600761493162416, 0.5893377471381324, 2.7776943024238743, 1.2953853864475096, 1.3430151489985716, 1.349220668411499, 1.387106912693971, 0.6786627901357709, 1.3709857269743364, 0.6174476585752983], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b7b59d550&gt;: [0.657116516034601, 0.6483388930693321, 0.6874968974135953, 0.5869423257563177, 0.7424460835172106, 0.6492716355124545, 0.6555588125501545, 0.6108199345953751, 0.6914517992255925, 0.6729277996394024, 0.6730225068847274, 0.6239628194206392, 0.695329581005431, 0.6224383331552714, 0.6905698389395983, 0.6280876209601857, 0.6564539116316079, 0.6861067859336422, 0.6835216310369522, 0.6471335644444782], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5b82f6f050&gt;: [0.6721609583901708, 0.6498461860804418, 0.6627063810000862, 0.5786714498881284, 0.7447016037179743, 0.6382281382931776, 0.6523809131970595, 0.6157133742548676, 0.6622423100141461, 0.6263203988658708, 0.6821167461805193, 0.5958446820924022, 0.6868592033649312, 0.6075218295903162, 0.6543695125575401, 0.6261707913569935, 0.6562027821399977, 0.6660761020084133, 0.6532629487495357, 0.6430158608370873], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b82f6d190&gt;: [1.9530391328462844, 2.1246233852733845, 0.5007592044610267, 1.4170971367205207, 3.2202319505592816, 1.4639961109350075, 0.24484587935292765, 1.5471325675646448, 2.4546071681628723, 1.5442328997834671, 2.473020824694054, 1.869433595295986, 0.5600362821776907, 0.4246463504451338, 0.348230021514094, 1.8549519395185856, 0.4872732735750704, 1.7533118761415492, 5.1288686415027005, 0.3196096923471954], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b81946750&gt;: [0.5188970392527981, 0.5012779482950143, 0.513426539414995, 0.2926496244840151, 0.4582599989717109, 0.3415477030377762, 0.2097356569718965, 0.3713731998563695, 0.7773348784458333, 0.3511482581324294, 0.5676929301841976, 0.20142467116511872, 0.558329821459328, 0.4088706873214252, 0.35531282810201326, 0.3960412731607384, 0.4342944765694567, 0.5156953930306226, 0.3354353482193721, 0.31074172637727837], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5b81947250&gt;: [0.42749233677310555, 0.6268740196903122, 0.5490502316236134, 0.3547468913667155, 0.539244973898371, 0.3947322087212688, 0.18265954695651268, 0.4633528452810814, 0.639915097526367, 0.3646502520788422, 0.49025427904929275, 0.19060503014555938, 0.5896268140520738, 0.4494149510238726, 0.35982558459297437, 0.5300711959747664, 0.5316700149780192, 0.35285666315201114, 2.0747964072807115, 0.3598385318027722], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b81945350&gt;: [0.5148711910566958, 0.5940185444538889, 0.5350898698214637, 0.46256349488868337, 0.5996782486157326, 0.542065790905018, 0.49331979460228437, 0.4538884272652949, 0.6289350820047499, 0.4787822218812146, 0.5223521664701753, 0.45127347046524346, 0.5385108127798727, 0.5848611105779689, 0.5182544666427298, 0.4373293302427228, 0.5030344516799756, 0.5723715812696119, 0.47451147233921814, 0.47584295832086215], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b81944c10&gt;: [0.7935545463068574, 0.6007216956589908, 0.7636881901626725, 0.6155288489650941, 0.8175789454011329, 0.6576888937547519, 0.7623583523463237, 0.6805934325759623, 0.7897605324510303, 0.6544287327455428, 0.6787232601899995, 0.6522488466429779, 0.8301174717464767, 0.6638644027030869, 0.681235355317911, 0.6856640954794676, 0.7560622789504617, 0.8097407006053563, 0.7772281943862416, 0.6609305822754844], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5b81945f90&gt;: [0.515004213042076, 0.5955617957076577, 0.5364233729424221, 0.4634492005184609, 0.6481370361204095, 0.5444134060606313, 0.49824209118110524, 0.473102312518728, 0.6498035173840981, 0.4790276646201193, 0.5426557682927409, 0.4323425682814415, 0.5633448525565664, 0.5875755695976448, 0.5171794144081898, 0.5241795316120872, 0.5460654460779927, 0.5753214372509369, 0.477303995880421, 0.4778760781769508], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b819454d0&gt;: [4.325238406694059, 8.09143239347528, 6.487857610041087, 5.8846781043456575, 5.7669845422587445, 8.827017156518487, 5.046111474476402, 3.6779238152160367, 9.371349881170461, 4.413508578259244, 5.046111474476402, 5.149093341302451, 7.929603745605773, 7.355847630432072, 6.487857610041087, 9.562601919561693, 8.650476813388117, 8.09143239347528, 6.487857610041087, 4.413508578259244], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b81945d50&gt;: [0.9685924334059304, 1.7936101012464158, 1.0368648314391447, 1.7711894422940055, 1.7286986713087424, 1.1784034310899174, 2.484364608452866, 0.999038159470634, 2.457681041253249, 1.0497505400785525, 2.448529419068306, 0.3235041670199816, 2.4370221361702344, 3.8917284228955245, 1.0101812642395271, 2.6530402844578704, 1.7438749556102886, 2.5326621915711622, 1.1176868323932105, 1.8125634329172884], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f5b81946f50&gt;: [0.4400068692157701, 1.1888717934943123, 1.1758077708996884, 1.1384129337026911, 1.1003973020365996, 0.4920037648365314, 0.4970915234413759, 0.4004244352379251, 0.4999215146868499, 1.133121452112281, 1.0905003286517425, 0.4458453342554336, 1.866350840346535, 1.86992775746637, 0.4164017436615977, 1.9495114408424843, 1.1350353799564967, 1.213093575870292, 0.5054492760035104, 0.4717563513746847]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82f6a8690&gt;: [0.49734468685013794, 1.339719662719736, 2.8317842177554273, 1.309201350604787, 1.4873233782225004, 1.3862225192263025, 2.783780909328769, 0.7541218268950224, 1.2660487961173514, 1.2414276668587374, 1.9934111898298519, 0.5277650227656568, 0.7258372828899489, 2.0303905683780292, 1.3960364143931432, 1.3352566178020868, 1.3953007299120217, 0.5725154355613066, 1.3575163584862002, 0.5624348487568565], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82c544110&gt;: [0.5733683079195263, 0.6380485617648682, 0.7057767291205743, 0.5987498857583323, 0.7152510361295089, 0.6931889977224969, 0.7295644431467594, 0.5938797826985205, 0.6306138194871087, 0.5640823354474354, 0.6381138695886015, 0.5488301309891347, 0.6634860715098427, 0.6003013944659328, 0.6592628703338441, 0.609282715687997, 0.6844383920181643, 0.6331176841936086, 0.7160956405437147, 0.5615455921247716], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fb82c54b9d0&gt;: [0.5920276683231201, 0.6221898768483168, 0.6639979889089485, 0.5883424100162901, 0.703255678942978, 0.6854396330727853, 0.7101167917829886, 0.5974594590718144, 0.6201443088902727, 0.5657075399313911, 0.6303075768166397, 0.5662168519188558, 0.6557209469063074, 0.5918253153771669, 0.6559718854671154, 0.6113061922005768, 0.6421429414101648, 0.5935814062064493, 0.70973494496844, 0.5681383071383924], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c547a90&gt;: [2.1239720585628983, 1.1631024754994728, 2.192893914256411, 0.24781912421095934, 3.2617886822986857, 2.0589703018895134, 0.4671764780891422, 0.2520375703150688, 0.4226571849179661, 7.156749601578534, 1.9542960297503351, 0.24164065226045914, 0.3963818790926276, 2.468842081178729, 2.3649381342477893, 0.28136128590131454, 7.09538039958095, 1.1169786664565997, 2.4967850370870663, 2.1825090261692077], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c54b650&gt;: [0.3099722050766103, 0.4828346925602213, 0.3607936931903034, 0.22179180583278443, 0.31992504778270786, 0.4738720596319454, 0.6551369658892885, 0.33401156265715404, 0.46384533259288985, 0.19241408863674678, 0.2447332230596978, 0.27566532527906634, 0.3873466260921623, 0.3076008656071076, 0.46348748797073525, 0.38594623924625443, 0.40864068373113666, 0.22883015133649687, 0.5798451759411164, 0.30252876512501775], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fb82c54b250&gt;: [0.31134739099413794, 0.48071409600083015, 0.45193151270991594, 0.26150843175355587, 0.35547158980494736, 0.5087957061988725, 0.611585894279742, 0.3727454786959005, 0.42214998145888394, 0.20165574612747816, 0.23532099717699992, 0.45742568764775626, 0.37411926857385575, 0.4323743130469052, 0.5280914310777098, 0.5049391069611963, 0.3711866177959071, 0.25602883347330607, 0.6520399429599284, 0.3507480468085061], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82c54b310&gt;: [0.47519191930476606, 0.5291686791543373, 0.5807171518851975, 0.42657004118157454, 0.42561888258579855, 0.6407785163395451, 0.5795607760630377, 0.4986736413264168, 0.48912070340574393, 0.4283082568760922, 0.48681638709408204, 0.4592384302580199, 0.5513524380123901, 0.4550144586956277, 0.6205856240507278, 0.43389157403470624, 0.49253893767531276, 0.4782848737210434, 0.6006468634753052, 0.48255223920607665], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82c54b3d0&gt;: [0.6862522607425858, 0.6360051677750004, 0.7020345845643315, 0.6520510986250133, 0.7245661818074072, 0.6124940967923451, 0.6988065392708481, 0.6811893740933945, 0.716355737438266, 0.6311188414780106, 0.6983252394430611, 0.5901839607989631, 0.6758223660601633, 0.6221364251303941, 0.657305656986902, 0.5439382056181856, 0.6915358891269934, 0.6350962109762246, 0.7354339196142625, 0.5893955676796764], &lt;method-wrapper \'__str__\' of SVC object at 0x7fb82c54b1d0&gt;: [0.45329858337897655, 0.5531084045292266, 0.5760299455631231, 0.4491962001771976, 0.44832045011209387, 0.6223925465572128, 0.5819564375914434, 0.49920696682934845, 0.4903478132378797, 0.428036452619491, 0.47473495839875895, 0.5108957172422792, 0.5526941166753493, 0.459010704531543, 0.6442449536693446, 0.4565831550669957, 0.4743856118669474, 0.5234757810423594, 0.6255768310611772, 0.46514166945933466], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82c54b110&gt;: [2.1626192033470297, 3.6779238152160367, 6.487857610041087, 2.9423390521728296, 4.325238406694059, 10.298186682604902, 6.487857610041087, 3.6779238152160367, 2.8834922711293727, 5.8846781043456575, 5.046111474476402, 2.9423390521728296, 5.7669845422587445, 5.149093341302451, 6.487857610041087, 6.620262867388865, 6.487857610041087, 5.149093341302451, 6.487857610041087, 8.091432393475278], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82c54afd0&gt;: [0.8702384874371907, 1.777060504997103, 2.407982908257489, 1.6932489318905593, 0.9743460748549659, 2.5905857784437574, 3.7976752501132878, 0.9459220434411568, 1.6465633296643296, 1.0769786698740809, 0.3575805944903984, 0.32590790244154044, 1.0159349056885627, 1.0390720065323373, 1.6871098404751461, 0.36247442222170484, 1.037907151461925, 1.7711894422940055, 3.046720634395419, 0.4062521482665457], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fb82c54ae50&gt;: [1.0361134444973228, 1.8526636605387696, 1.1559427354394827, 0.4172275523035351, 1.1404469120474736, 2.6504494087797927, 2.5866559186384444, 0.3608745989235143, 0.350259126209136, 0.4826653748518951, 0.4523531622718424, 0.49524060218707505, 1.1595665963077657, 0.41591043962725815, 1.1389076912247509, 0.4752236786562235, 0.4181508526680915, 1.1686013491471638, 1.784370290144005, 0.4773738932614852]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd2e4b790&gt;: [0.5856414837365413, 0.7250919316900355, 0.5959470832188487, 1.3600849957828987, 1.29978510678646, 0.5634207875632081, 0.6358410894833437, 0.5944698071844178, 1.9120877161247436, 0.7092765692075638, 0.6134564579659267, 0.6421581484717133, 0.571055759193025, 2.0458025209456987, 0.6516518800147155, 1.2770855081296806, 1.1606587698745288, 0.6096460914859642, 2.7378228664269755, 0.7138867123825228], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabd3855910&gt;: [0.5972358730916402, 0.6328914601088855, 0.590370884918053, 0.6256098788273986, 0.5662004851016829, 0.6580746326826378, 0.6062845931368911, 0.5995713491489729, 0.6203258071392106, 0.6375354587883915, 0.5981412063969507, 0.701079237207658, 0.55733027859421, 0.6063014171855587, 0.5992343389372775, 0.5682246784120291, 0.5014161976998974, 0.6159498829131902, 0.6741812229103425, 0.6182418426221777], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fabdd3df910&gt;: [0.5933750296992194, 0.6228278644688118, 0.5917717500247542, 0.6310898666344565, 0.5623530164791923, 0.6245365152020566, 0.5918960412692743, 0.604043685406232, 0.6039250878944042, 0.6013960762794497, 0.6013082406124186, 0.6415836607611936, 0.5638606042919696, 0.5724190676949306, 0.5895075708759675, 0.5842657298524842, 0.5324029289587638, 0.6187286020095197, 0.6898214120237145, 0.5883980477158073], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabd220bcd0&gt;: [1.4808273757506865, 3.072607080730232, 1.1891724927243283, 8.97880215035485, 7.980975536886099, 1.6768485141743454, 7.156671393373299, 1.7449501618668741, 1.6991884616509072, 7.598226219108242, 0.9447235103349441, 3.3150142761204777, 8.741212237004685, 1.5732094547915123, 6.760973131133864, 1.5277473295893917, 1.2567971096942614, 6.870940069612035, 2.2121112050941356, 1.1751221014150923], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd5a1990&gt;: [0.24586445306319288, 0.481340189873127, 0.20125770563741713, 0.31012256631196, 0.17805054603202086, 0.610457249971592, 0.1492721951061168, 0.518014504252028, 0.3798435667183917, 0.18729060851647975, 0.18979382568596176, 0.5104101924537939, 0.23224659991084884, 0.33836390499781444, 0.3348800760828217, 0.3109425478491237, 0.30369362205150074, 1.148544596835654, 0.46724103281024076, 0.20618416261439532], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fabdd5a3f90&gt;: [0.36063384668679327, 0.6057454326349585, 0.20717065545300656, 0.3630307784548838, 0.16841003808768892, 0.8140953575425931, 0.06882434987507274, 0.5652535851444035, 0.4268401287791071, 0.21955297779144328, 0.35683918335747833, 0.6774983274555137, 0.25280919107234734, 0.41221820361137446, 0.49808617794841387, 0.3867821876944614, 0.3767180029183132, 0.37605412488100753, 0.5375571636839322, 0.22914042909294377], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabd2e4a510&gt;: [0.4517750913638237, 0.5955981830076421, 0.3886806480254702, 0.4789018883688647, 0.4104526027640095, 0.6267276408848186, 0.43043283677373756, 0.5417135191088448, 0.4899817752743998, 0.4513490813961021, 0.4281257901663812, 0.5241182388454134, 0.4335836751925286, 0.49551985088012573, 0.4090789883707884, 0.4929889860348371, 0.45389063492159337, 0.5172972720039488, 0.5525583703922979, 0.46990668993867096], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd5a1250&gt;: [0.6039504031253484, 0.6383490520292063, 0.609314087495594, 0.5726903596857398, 0.6211732715472355, 0.6072099767246201, 0.6252229367976896, 0.6114888913237642, 0.6091442455608155, 0.5646646794258183, 0.5615963783484232, 0.6349552836044504, 0.6268220917704358, 0.5453661169574004, 0.6324128850413733, 0.6751530930117036, 0.6299675373960522, 0.6078142135761574, 0.6366436166708476, 0.638145951810028], &lt;method-wrapper \'__str__\' of SVC object at 0x7fabdd5a1210&gt;: [0.4520154958854271, 0.5936358383961282, 0.4110338054494191, 0.47834795404912506, 0.41081394094341783, 0.6039859042637117, 0.4304912520494883, 0.5413268337619166, 0.4683601926628685, 0.4517189920379083, 0.44848968153939334, 0.5243750982587178, 0.4526654942378729, 0.47811952455027884, 0.4090924640635646, 0.47356022861939956, 0.45418791676648057, 0.5185591095435942, 0.5542205265540343, 0.4496367409748329], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabd38550d0&gt;: [5.046111474476402, 5.7669845422587445, 5.046111474476402, 4.325238406694059, 1.4417461355646868, 8.650476813388117, 5.7669845422587445, 4.325238406694059, 5.046111474476402, 7.20873067782343, 6.487857610041087, 3.604365338911716, 3.604365338911716, 4.325238406694059, 3.604365338911716, 4.325238406694059, 8.650476813388117, 4.325238406694059, 5.7669845422587445, 5.046111474476402], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd5a3150&gt;: [0.2778009135591129, 2.386010662484127, 1.0368648314391447, 0.9800997163040017, 0.23385642201238852, 1.7286986713087424, 1.7161490683878913, 2.355929114548601, 1.7148357276975437, 1.0496854550275634, 1.6952191426373093, 2.3467774923636577, 1.0277132092542012, 0.9662367726928026, 1.0760980015596138, 1.763491540670523, 1.0091389442167469, 2.3998736060953254, 3.140363258937904, 1.1142888516573026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fabdd5a1950&gt;: [0.423065483959126, 2.5175670807148243, 0.4175602929100616, 1.120830326987239, 0.3314589810393066, 1.1373684704020284, 0.4403489785738288, 1.801156883958766, 0.37562935271840614, 0.42469836373993625, 1.0742817243274156, 2.4291101081309416, 1.1205818765872677, 0.4258954752046001, 0.48347703023014815, 0.4078181109670881, 1.089777547719425, 1.8299476614715398, 2.495026845451028, 0.43482121725716844]}'}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
     <t>{0: 'SVC(random_state=13)WITHOUT log_loss_field', 1: 'SVC(random_state=13)WITHOUT log_loss_field', 2: 'SVC(random_state=13)WITHOUT log_loss_field', 3: 'SVC(random_state=13)WITHOUT log_loss_field', 4: 'SVC(random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 1: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 2: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 3: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 4: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field'}</t>
@@ -699,40 +675,40 @@
         <v>48</v>
       </c>
       <c r="F2">
-        <v>0.975601851851852</v>
+        <v>0.9841666666666666</v>
       </c>
       <c r="G2">
-        <v>0.0187174500273974</v>
+        <v>0.0267641447545862</v>
       </c>
       <c r="H2">
-        <v>0.9186666666666665</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I2">
-        <v>0.05848456586523014</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J2">
-        <v>0.8934722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K2">
-        <v>0.07410161525038475</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L2">
-        <v>0.9404671717171718</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M2">
-        <v>0.05485947650155152</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N2">
-        <v>0.8934722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O2">
-        <v>0.07410161525038475</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P2">
-        <v>0.9080966900316746</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q2">
-        <v>0.06787736387451176</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
@@ -749,40 +725,40 @@
         <v>48</v>
       </c>
       <c r="F3">
-        <v>0.975601851851852</v>
+        <v>0.9841666666666666</v>
       </c>
       <c r="G3">
-        <v>0.0187174500273974</v>
+        <v>0.0267641447545862</v>
       </c>
       <c r="H3">
-        <v>0.9186666666666665</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I3">
-        <v>0.05848456586523014</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J3">
-        <v>0.8934722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K3">
-        <v>0.07410161525038475</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L3">
-        <v>0.9404671717171718</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M3">
-        <v>0.05485947650155152</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N3">
-        <v>0.8934722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O3">
-        <v>0.07410161525038475</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P3">
-        <v>0.9080966900316746</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q3">
-        <v>0.06787736387451176</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R3" t="s">
         <v>50</v>
@@ -799,40 +775,40 @@
         <v>48</v>
       </c>
       <c r="F4">
-        <v>0.975601851851852</v>
+        <v>0.9841666666666666</v>
       </c>
       <c r="G4">
-        <v>0.0187174500273974</v>
+        <v>0.0267641447545862</v>
       </c>
       <c r="H4">
-        <v>0.9186666666666665</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I4">
-        <v>0.05848456586523014</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J4">
-        <v>0.8934722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K4">
-        <v>0.07410161525038475</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L4">
-        <v>0.9404671717171718</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M4">
-        <v>0.05485947650155152</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N4">
-        <v>0.8934722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O4">
-        <v>0.07410161525038475</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P4">
-        <v>0.9080966900316746</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q4">
-        <v>0.06787736387451176</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R4" t="s">
         <v>51</v>
@@ -842,47 +818,41 @@
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
       <c r="F5">
-        <v>0.975216049382716</v>
+        <v>0.9808333333333333</v>
       </c>
       <c r="G5">
-        <v>0.01733756290505286</v>
+        <v>0.02138437903392724</v>
       </c>
       <c r="H5">
-        <v>0.9106666666666665</v>
+        <v>0.8923076923076924</v>
       </c>
       <c r="I5">
-        <v>0.04873511168665882</v>
+        <v>0.0923076923076923</v>
       </c>
       <c r="J5">
-        <v>0.8809722222222222</v>
+        <v>0.85</v>
       </c>
       <c r="K5">
-        <v>0.05650166609583245</v>
+        <v>0.1286953767623375</v>
       </c>
       <c r="L5">
-        <v>0.9330050505050507</v>
+        <v>0.8341666666666667</v>
       </c>
       <c r="M5">
-        <v>0.04954081761989716</v>
+        <v>0.1660488549259591</v>
       </c>
       <c r="N5">
-        <v>0.8809722222222222</v>
+        <v>0.85</v>
       </c>
       <c r="O5">
-        <v>0.05650166609583245</v>
+        <v>0.1286953767623375</v>
       </c>
       <c r="P5">
-        <v>0.8975700894392846</v>
+        <v>0.8350757575757577</v>
       </c>
       <c r="Q5">
-        <v>0.05489777519611348</v>
+        <v>0.1477780798411683</v>
       </c>
       <c r="R5" t="s">
         <v>52</v>
@@ -890,49 +860,49 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
         <v>48</v>
       </c>
       <c r="F6">
-        <v>0.9745987654320988</v>
+        <v>0.9766666666666668</v>
       </c>
       <c r="G6">
-        <v>0.01726819442761228</v>
+        <v>0.04165416479110399</v>
       </c>
       <c r="H6">
-        <v>0.9106666666666665</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I6">
-        <v>0.04873511168665882</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J6">
-        <v>0.8809722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K6">
-        <v>0.05650166609583245</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L6">
-        <v>0.9330050505050507</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M6">
-        <v>0.04954081761989716</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N6">
-        <v>0.8809722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O6">
-        <v>0.05650166609583245</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P6">
-        <v>0.8975700894392846</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q6">
-        <v>0.05489777519611348</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R6" t="s">
         <v>53</v>
@@ -940,49 +910,49 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
       </c>
       <c r="F7">
-        <v>0.9745987654320988</v>
+        <v>0.9766666666666668</v>
       </c>
       <c r="G7">
-        <v>0.01726819442761228</v>
+        <v>0.04165416479110399</v>
       </c>
       <c r="H7">
-        <v>0.9106666666666665</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I7">
-        <v>0.04873511168665882</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J7">
-        <v>0.8809722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K7">
-        <v>0.05650166609583245</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L7">
-        <v>0.9330050505050507</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M7">
-        <v>0.04954081761989716</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N7">
-        <v>0.8809722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O7">
-        <v>0.05650166609583245</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P7">
-        <v>0.8975700894392846</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q7">
-        <v>0.05489777519611348</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R7" t="s">
         <v>54</v>
@@ -993,46 +963,46 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
       </c>
       <c r="F8">
-        <v>0.9722608024691357</v>
+        <v>0.9766666666666668</v>
       </c>
       <c r="G8">
-        <v>0.02147716294216966</v>
+        <v>0.04165416479110399</v>
       </c>
       <c r="H8">
-        <v>0.9106666666666665</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I8">
-        <v>0.04873511168665882</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J8">
-        <v>0.8879166666666667</v>
+        <v>0.9375</v>
       </c>
       <c r="K8">
-        <v>0.06656473689222296</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L8">
-        <v>0.9304671717171716</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M8">
-        <v>0.04710526081413537</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N8">
-        <v>0.8879166666666667</v>
+        <v>0.9375</v>
       </c>
       <c r="O8">
-        <v>0.06656473689222296</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P8">
-        <v>0.8995999580055308</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q8">
-        <v>0.05774390662932569</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R8" t="s">
         <v>55</v>
@@ -1043,46 +1013,46 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
       </c>
       <c r="F9">
-        <v>0.9722608024691357</v>
+        <v>0.9766666666666668</v>
       </c>
       <c r="G9">
-        <v>0.02147716294216966</v>
+        <v>0.04165416479110399</v>
       </c>
       <c r="H9">
-        <v>0.9106666666666665</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I9">
-        <v>0.04873511168665882</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J9">
-        <v>0.8879166666666667</v>
+        <v>0.9375</v>
       </c>
       <c r="K9">
-        <v>0.06656473689222296</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L9">
-        <v>0.9304671717171716</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M9">
-        <v>0.04710526081413537</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N9">
-        <v>0.8879166666666667</v>
+        <v>0.9375</v>
       </c>
       <c r="O9">
-        <v>0.06656473689222296</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P9">
-        <v>0.8995999580055308</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q9">
-        <v>0.05774390662932569</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R9" t="s">
         <v>56</v>
@@ -1090,43 +1060,49 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>0.9719560185185184</v>
+        <v>0.9766666666666668</v>
       </c>
       <c r="G10">
-        <v>0.01650966106883122</v>
+        <v>0.04165416479110399</v>
       </c>
       <c r="H10">
-        <v>0.8626666666666667</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I10">
-        <v>0.03309246305597564</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J10">
-        <v>0.8643055555555554</v>
+        <v>0.9375</v>
       </c>
       <c r="K10">
-        <v>0.02020630478554701</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L10">
-        <v>0.8720833333333333</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M10">
-        <v>0.04772687857247325</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N10">
-        <v>0.8643055555555554</v>
+        <v>0.9375</v>
       </c>
       <c r="O10">
-        <v>0.02020630478554701</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P10">
-        <v>0.8567955818691113</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q10">
-        <v>0.02994855785413787</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R10" t="s">
         <v>57</v>
@@ -1134,351 +1110,351 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
       </c>
       <c r="F11">
-        <v>0.9717901234567901</v>
+        <v>0.9766666666666668</v>
       </c>
       <c r="G11">
-        <v>0.0147900867443226</v>
+        <v>0.04165416479110399</v>
       </c>
       <c r="H11">
-        <v>0.9026666666666667</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="I11">
-        <v>0.04291593850514953</v>
+        <v>0.06153846153846153</v>
       </c>
       <c r="J11">
-        <v>0.8684722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K11">
-        <v>0.05162034960969524</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L11">
-        <v>0.9304671717171716</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="M11">
-        <v>0.04710526081413537</v>
+        <v>0.04146618434874909</v>
       </c>
       <c r="N11">
-        <v>0.8684722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O11">
-        <v>0.05162034960969524</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P11">
-        <v>0.8858744678094524</v>
+        <v>0.9440656565656566</v>
       </c>
       <c r="Q11">
-        <v>0.04998053235391143</v>
+        <v>0.07087327147904084</v>
       </c>
       <c r="R11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
       </c>
       <c r="F12">
-        <v>0.9717901234567901</v>
+        <v>0.9766666666666668</v>
       </c>
       <c r="G12">
-        <v>0.0147900867443226</v>
+        <v>0.04165416479110399</v>
       </c>
       <c r="H12">
-        <v>0.9026666666666667</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="I12">
-        <v>0.04291593850514953</v>
+        <v>0.05756395979652218</v>
       </c>
       <c r="J12">
-        <v>0.8684722222222222</v>
+        <v>0.925</v>
       </c>
       <c r="K12">
-        <v>0.05162034960969524</v>
+        <v>0.07288689868556625</v>
       </c>
       <c r="L12">
-        <v>0.9304671717171716</v>
+        <v>0.9525</v>
       </c>
       <c r="M12">
-        <v>0.04710526081413537</v>
+        <v>0.04245913067618999</v>
       </c>
       <c r="N12">
-        <v>0.8684722222222222</v>
+        <v>0.925</v>
       </c>
       <c r="O12">
-        <v>0.05162034960969524</v>
+        <v>0.07288689868556625</v>
       </c>
       <c r="P12">
-        <v>0.8858744678094524</v>
+        <v>0.9269227994227995</v>
       </c>
       <c r="Q12">
-        <v>0.04998053235391143</v>
+        <v>0.06542768448045932</v>
       </c>
       <c r="R12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="F13">
-        <v>0.9717901234567901</v>
+        <v>0.9766666666666666</v>
       </c>
       <c r="G13">
-        <v>0.0147900867443226</v>
+        <v>0.03401388605326426</v>
       </c>
       <c r="H13">
-        <v>0.9026666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I13">
-        <v>0.04291593850514953</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J13">
-        <v>0.8684722222222222</v>
+        <v>0.95</v>
       </c>
       <c r="K13">
-        <v>0.05162034960969524</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L13">
-        <v>0.9304671717171716</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M13">
-        <v>0.04710526081413537</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N13">
-        <v>0.8684722222222222</v>
+        <v>0.95</v>
       </c>
       <c r="O13">
-        <v>0.05162034960969524</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P13">
-        <v>0.8858744678094524</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q13">
-        <v>0.04998053235391143</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R13" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
         <v>48</v>
       </c>
       <c r="F14">
-        <v>0.9715046296296297</v>
+        <v>0.9766666666666666</v>
       </c>
       <c r="G14">
-        <v>0.02210331807887727</v>
+        <v>0.03401388605326426</v>
       </c>
       <c r="H14">
-        <v>0.9106666666666665</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I14">
-        <v>0.04873511168665882</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J14">
-        <v>0.8879166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K14">
-        <v>0.06656473689222296</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L14">
-        <v>0.9174368686868688</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M14">
-        <v>0.05350563187728459</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N14">
-        <v>0.8879166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O14">
-        <v>0.06656473689222296</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P14">
-        <v>0.895272472625414</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q14">
-        <v>0.05962479198279733</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="F15">
-        <v>0.9713425925925925</v>
+        <v>0.9766666666666666</v>
       </c>
       <c r="G15">
-        <v>0.02257123687089456</v>
+        <v>0.03401388605326426</v>
       </c>
       <c r="H15">
-        <v>0.9189999999999999</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I15">
-        <v>0.03693237062523876</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J15">
-        <v>0.9045833333333333</v>
+        <v>0.95</v>
       </c>
       <c r="K15">
-        <v>0.04325134694255985</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L15">
-        <v>0.9345580808080808</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M15">
-        <v>0.03931096383147397</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N15">
-        <v>0.9045833333333333</v>
+        <v>0.95</v>
       </c>
       <c r="O15">
-        <v>0.04325134694255985</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P15">
-        <v>0.9119683790581623</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q15">
-        <v>0.03770745497006488</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>0.9713104423868313</v>
+        <v>0.9764583333333334</v>
       </c>
       <c r="G16">
-        <v>0.0164654300703237</v>
+        <v>0.01947220240924651</v>
       </c>
       <c r="H16">
-        <v>0.8620000000000001</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="I16">
-        <v>0.06337191807101945</v>
+        <v>0.08426500884694865</v>
       </c>
       <c r="J16">
-        <v>0.8344444444444445</v>
+        <v>0.7925</v>
       </c>
       <c r="K16">
-        <v>0.08614537848641621</v>
+        <v>0.0687386354243376</v>
       </c>
       <c r="L16">
-        <v>0.8656944444444445</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="M16">
-        <v>0.06921573449176545</v>
+        <v>0.1344329655338386</v>
       </c>
       <c r="N16">
-        <v>0.8344444444444445</v>
+        <v>0.7925</v>
       </c>
       <c r="O16">
-        <v>0.08614537848641621</v>
+        <v>0.0687386354243376</v>
       </c>
       <c r="P16">
-        <v>0.8435497835497836</v>
+        <v>0.7889646464646465</v>
       </c>
       <c r="Q16">
-        <v>0.07943274765926497</v>
+        <v>0.0905676669440265</v>
       </c>
       <c r="R16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="F17">
-        <v>0.9712885802469134</v>
+        <v>0.97625</v>
       </c>
       <c r="G17">
-        <v>0.02378491965964936</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="H17">
-        <v>0.9106666666666665</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I17">
-        <v>0.04873511168665882</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J17">
-        <v>0.8879166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K17">
-        <v>0.06656473689222296</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L17">
-        <v>0.9304671717171716</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M17">
-        <v>0.04710526081413537</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N17">
-        <v>0.8879166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O17">
-        <v>0.06656473689222296</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P17">
-        <v>0.8995999580055308</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q17">
-        <v>0.05774390662932569</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
         <v>42</v>
@@ -1487,40 +1463,40 @@
         <v>48</v>
       </c>
       <c r="F18">
-        <v>0.9711676954732511</v>
+        <v>0.97625</v>
       </c>
       <c r="G18">
-        <v>0.01564190160236649</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="H18">
-        <v>0.8946666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I18">
-        <v>0.04266666666666665</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J18">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K18">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L18">
-        <v>0.913800505050505</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M18">
-        <v>0.05175830784892948</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N18">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O18">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P18">
-        <v>0.8781713865769595</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q18">
-        <v>0.05185520991559336</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R18" t="s">
         <v>62</v>
@@ -1528,49 +1504,49 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="F19">
-        <v>0.9692361111111112</v>
+        <v>0.97625</v>
       </c>
       <c r="G19">
-        <v>0.02422367159272305</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="H19">
-        <v>0.9106666666666665</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I19">
-        <v>0.04873511168665882</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J19">
-        <v>0.8809722222222222</v>
+        <v>0.95</v>
       </c>
       <c r="K19">
-        <v>0.05650166609583245</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L19">
-        <v>0.9330050505050507</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M19">
-        <v>0.04954081761989716</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N19">
-        <v>0.8809722222222222</v>
+        <v>0.95</v>
       </c>
       <c r="O19">
-        <v>0.05650166609583245</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P19">
-        <v>0.8975700894392846</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q19">
-        <v>0.05489777519611348</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R19" t="s">
         <v>62</v>
@@ -1578,257 +1554,245 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="F20">
-        <v>0.9688683127572016</v>
+        <v>0.97625</v>
       </c>
       <c r="G20">
-        <v>0.02448842441179914</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="H20">
-        <v>0.9106666666666665</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I20">
-        <v>0.04873511168665882</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J20">
-        <v>0.8879166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K20">
-        <v>0.06656473689222296</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L20">
-        <v>0.9304671717171716</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M20">
-        <v>0.04710526081413537</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N20">
-        <v>0.8879166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O20">
-        <v>0.06656473689222296</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P20">
-        <v>0.8995999580055308</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q20">
-        <v>0.05774390662932569</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="F21">
-        <v>0.9686213991769547</v>
+        <v>0.97625</v>
       </c>
       <c r="G21">
-        <v>0.01642643639060851</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="H21">
-        <v>0.8946666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I21">
-        <v>0.04266666666666665</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J21">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K21">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L21">
-        <v>0.913800505050505</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M21">
-        <v>0.05175830784892948</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N21">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O21">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P21">
-        <v>0.8781713865769595</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q21">
-        <v>0.05185520991559336</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="F22">
-        <v>0.9685558127572016</v>
+        <v>0.97625</v>
       </c>
       <c r="G22">
-        <v>0.02518321997971835</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="H22">
-        <v>0.9189999999999999</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I22">
-        <v>0.03693237062523876</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J22">
-        <v>0.9045833333333333</v>
+        <v>0.95</v>
       </c>
       <c r="K22">
-        <v>0.04325134694255985</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L22">
-        <v>0.9345580808080808</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M22">
-        <v>0.03931096383147397</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N22">
-        <v>0.9045833333333333</v>
+        <v>0.95</v>
       </c>
       <c r="O22">
-        <v>0.04325134694255985</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P22">
-        <v>0.9119683790581623</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q22">
-        <v>0.03770745497006488</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>0.968503086419753</v>
+        <v>0.975</v>
       </c>
       <c r="G23">
-        <v>0.02367900299228045</v>
+        <v>0.04693745838879648</v>
       </c>
       <c r="H23">
-        <v>0.9106666666666665</v>
+        <v>0.953846153846154</v>
       </c>
       <c r="I23">
-        <v>0.04873511168665882</v>
+        <v>0.03768445758127963</v>
       </c>
       <c r="J23">
-        <v>0.8809722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K23">
-        <v>0.05650166609583245</v>
+        <v>0.05590169943749474</v>
       </c>
       <c r="L23">
-        <v>0.9330050505050507</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="M23">
-        <v>0.04954081761989716</v>
+        <v>0.0219848432637882</v>
       </c>
       <c r="N23">
-        <v>0.8809722222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O23">
-        <v>0.05650166609583245</v>
+        <v>0.05590169943749474</v>
       </c>
       <c r="P23">
-        <v>0.8975700894392846</v>
+        <v>0.9448773448773448</v>
       </c>
       <c r="Q23">
-        <v>0.05489777519611348</v>
+        <v>0.04861565876240073</v>
       </c>
       <c r="R23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F24">
-        <v>0.9680941358024692</v>
+        <v>0.975</v>
       </c>
       <c r="G24">
-        <v>0.02376385376352606</v>
+        <v>0.04693745838879648</v>
       </c>
       <c r="H24">
-        <v>0.9106666666666665</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="I24">
-        <v>0.04873511168665882</v>
+        <v>0.05756395979652217</v>
       </c>
       <c r="J24">
-        <v>0.8809722222222222</v>
+        <v>0.9425000000000001</v>
       </c>
       <c r="K24">
-        <v>0.05650166609583245</v>
+        <v>0.0687386354243376</v>
       </c>
       <c r="L24">
-        <v>0.9330050505050507</v>
+        <v>0.9358333333333334</v>
       </c>
       <c r="M24">
-        <v>0.04954081761989716</v>
+        <v>0.06930207628763931</v>
       </c>
       <c r="N24">
-        <v>0.8809722222222222</v>
+        <v>0.9425000000000001</v>
       </c>
       <c r="O24">
-        <v>0.05650166609583245</v>
+        <v>0.0687386354243376</v>
       </c>
       <c r="P24">
-        <v>0.8975700894392846</v>
+        <v>0.9358333333333334</v>
       </c>
       <c r="Q24">
-        <v>0.05489777519611348</v>
+        <v>0.06885527853923799</v>
       </c>
       <c r="R24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>41</v>
@@ -1837,707 +1801,719 @@
         <v>48</v>
       </c>
       <c r="F25">
-        <v>0.9675102880658436</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G25">
-        <v>0.01670658355626631</v>
+        <v>0.03462096346306832</v>
       </c>
       <c r="H25">
-        <v>0.8946666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I25">
-        <v>0.04266666666666665</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J25">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K25">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L25">
-        <v>0.913800505050505</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M25">
-        <v>0.05175830784892948</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N25">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O25">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P25">
-        <v>0.8781713865769595</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q25">
-        <v>0.05185520991559336</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R25" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="F26">
-        <v>0.9674729938271603</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G26">
-        <v>0.02065670294418151</v>
+        <v>0.03462096346306832</v>
       </c>
       <c r="H26">
-        <v>0.9189999999999999</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I26">
-        <v>0.03693237062523876</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J26">
-        <v>0.8865277777777777</v>
+        <v>0.95</v>
       </c>
       <c r="K26">
-        <v>0.04657563873375</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L26">
-        <v>0.9503661616161617</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M26">
-        <v>0.02071878518112718</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N26">
-        <v>0.8865277777777777</v>
+        <v>0.95</v>
       </c>
       <c r="O26">
-        <v>0.04657563873375</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P26">
-        <v>0.9075047299621604</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q26">
-        <v>0.03769890321720803</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R26" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="F27">
-        <v>0.9670563271604939</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G27">
-        <v>0.02225515312272478</v>
+        <v>0.03462096346306832</v>
       </c>
       <c r="H27">
-        <v>0.9189999999999999</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I27">
-        <v>0.03693237062523876</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J27">
-        <v>0.8865277777777777</v>
+        <v>0.95</v>
       </c>
       <c r="K27">
-        <v>0.04657563873375</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L27">
-        <v>0.9503661616161617</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M27">
-        <v>0.02071878518112718</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N27">
-        <v>0.8865277777777777</v>
+        <v>0.95</v>
       </c>
       <c r="O27">
-        <v>0.04657563873375</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P27">
-        <v>0.9075047299621604</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q27">
-        <v>0.03769890321720803</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R27" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="F28">
-        <v>0.9668158436213992</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G28">
-        <v>0.01741923588043983</v>
+        <v>0.03462096346306832</v>
       </c>
       <c r="H28">
-        <v>0.9026666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I28">
-        <v>0.04291593850514953</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J28">
-        <v>0.8754166666666666</v>
+        <v>0.95</v>
       </c>
       <c r="K28">
-        <v>0.05429756263997473</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L28">
-        <v>0.9093813131313132</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M28">
-        <v>0.05096854242678027</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N28">
-        <v>0.8754166666666666</v>
+        <v>0.95</v>
       </c>
       <c r="O28">
-        <v>0.05429756263997473</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P28">
-        <v>0.8853868517103812</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q28">
-        <v>0.05210930119256825</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R28" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="F29">
-        <v>0.9668158436213992</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G29">
-        <v>0.01607543127236588</v>
+        <v>0.03462096346306832</v>
       </c>
       <c r="H29">
-        <v>0.8946666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I29">
-        <v>0.04266666666666665</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J29">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K29">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L29">
-        <v>0.913800505050505</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M29">
-        <v>0.05175830784892948</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N29">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O29">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P29">
-        <v>0.8781713865769595</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q29">
-        <v>0.05185520991559336</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R29" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="F30">
-        <v>0.9659053497942386</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G30">
-        <v>0.01691617866005617</v>
+        <v>0.03462096346306832</v>
       </c>
       <c r="H30">
-        <v>0.8946666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I30">
-        <v>0.04266666666666665</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J30">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K30">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L30">
-        <v>0.913800505050505</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M30">
-        <v>0.05175830784892948</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N30">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O30">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P30">
-        <v>0.8781713865769595</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q30">
-        <v>0.05185520991559336</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R30" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
       </c>
       <c r="F31">
-        <v>0.9653472222222221</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G31">
-        <v>0.02041918603755338</v>
+        <v>0.03462096346306832</v>
       </c>
       <c r="H31">
-        <v>0.9023333333333333</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I31">
-        <v>0.06278357888634399</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J31">
-        <v>0.8754166666666666</v>
+        <v>0.95</v>
       </c>
       <c r="K31">
-        <v>0.06872347973339732</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L31">
-        <v>0.9490620490620492</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M31">
-        <v>0.02419357710202256</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N31">
-        <v>0.8754166666666666</v>
+        <v>0.95</v>
       </c>
       <c r="O31">
-        <v>0.06872347973339732</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P31">
-        <v>0.8976332872792693</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q31">
-        <v>0.05689794916310915</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R31" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F32">
-        <v>0.9653356481481481</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G32">
-        <v>0.02032705305932999</v>
+        <v>0.04469029225930642</v>
       </c>
       <c r="H32">
-        <v>0.9189999999999999</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="I32">
-        <v>0.03693237062523876</v>
+        <v>0.07536891516255934</v>
       </c>
       <c r="J32">
-        <v>0.8865277777777777</v>
+        <v>0.9375</v>
       </c>
       <c r="K32">
-        <v>0.04657563873375</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L32">
-        <v>0.9503661616161617</v>
+        <v>0.9375</v>
       </c>
       <c r="M32">
-        <v>0.02071878518112718</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="N32">
-        <v>0.8865277777777777</v>
+        <v>0.9375</v>
       </c>
       <c r="O32">
-        <v>0.04657563873375</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P32">
-        <v>0.9075047299621604</v>
+        <v>0.9312878787878788</v>
       </c>
       <c r="Q32">
-        <v>0.03769890321720803</v>
+        <v>0.08474005517658986</v>
       </c>
       <c r="R32" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F33">
-        <v>0.9646013374485596</v>
+        <v>0.9745833333333334</v>
       </c>
       <c r="G33">
-        <v>0.02538773642415887</v>
+        <v>0.04469029225930642</v>
       </c>
       <c r="H33">
-        <v>0.8626666666666667</v>
+        <v>0.9076923076923077</v>
       </c>
       <c r="I33">
-        <v>0.04165466493816881</v>
+        <v>0.08970695222838923</v>
       </c>
       <c r="J33">
-        <v>0.8629166666666667</v>
+        <v>0.9175000000000001</v>
       </c>
       <c r="K33">
-        <v>0.03500606208524532</v>
+        <v>0.08276472678623424</v>
       </c>
       <c r="L33">
-        <v>0.8968885281385282</v>
+        <v>0.9108333333333333</v>
       </c>
       <c r="M33">
-        <v>0.04195768248627656</v>
+        <v>0.0812061847671989</v>
       </c>
       <c r="N33">
-        <v>0.8629166666666667</v>
+        <v>0.9175000000000001</v>
       </c>
       <c r="O33">
-        <v>0.03500606208524532</v>
+        <v>0.08276472678623424</v>
       </c>
       <c r="P33">
-        <v>0.8694447292473606</v>
+        <v>0.9036111111111111</v>
       </c>
       <c r="Q33">
-        <v>0.03110244121951677</v>
+        <v>0.09131920680154969</v>
       </c>
       <c r="R33" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
       </c>
       <c r="F34">
-        <v>0.9646013374485596</v>
+        <v>0.9741666666666667</v>
       </c>
       <c r="G34">
-        <v>0.02538773642415887</v>
+        <v>0.04663317250389232</v>
       </c>
       <c r="H34">
-        <v>0.8623333333333333</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I34">
-        <v>0.05628893714083118</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J34">
-        <v>0.8649999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="K34">
-        <v>0.03695227569463546</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L34">
-        <v>0.8634108946608947</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M34">
-        <v>0.06245579999985572</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N34">
-        <v>0.8649999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="O34">
-        <v>0.03695227569463546</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P34">
-        <v>0.8530116288939817</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q34">
-        <v>0.04909741150691439</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R34" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
       </c>
       <c r="F35">
-        <v>0.9636586934156378</v>
+        <v>0.9741666666666667</v>
       </c>
       <c r="G35">
-        <v>0.02934444570694879</v>
+        <v>0.04663317250389232</v>
       </c>
       <c r="H35">
-        <v>0.8783333333333333</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I35">
-        <v>0.05897268670984711</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J35">
-        <v>0.8736111111111111</v>
+        <v>0.95</v>
       </c>
       <c r="K35">
-        <v>0.04216141454627929</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L35">
-        <v>0.9088492063492064</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M35">
-        <v>0.05075233935110259</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N35">
-        <v>0.8736111111111111</v>
+        <v>0.95</v>
       </c>
       <c r="O35">
-        <v>0.04216141454627929</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P35">
-        <v>0.879851316124536</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q35">
-        <v>0.04388692111223848</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R35" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" t="s">
+        <v>48</v>
       </c>
       <c r="F36">
-        <v>0.9636586934156378</v>
+        <v>0.9741666666666667</v>
       </c>
       <c r="G36">
-        <v>0.02934444570694879</v>
+        <v>0.04663317250389232</v>
       </c>
       <c r="H36">
-        <v>0.8546666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I36">
-        <v>0.04139779919002674</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J36">
-        <v>0.8691666666666666</v>
+        <v>0.95</v>
       </c>
       <c r="K36">
-        <v>0.02606008607851772</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L36">
-        <v>0.8551767676767676</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M36">
-        <v>0.02772492676502698</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N36">
-        <v>0.8691666666666666</v>
+        <v>0.95</v>
       </c>
       <c r="O36">
-        <v>0.02606008607851772</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P36">
-        <v>0.8467215219421101</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q36">
-        <v>0.02621130997536347</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R36" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
         <v>48</v>
       </c>
       <c r="F37">
-        <v>0.9615727880658435</v>
+        <v>0.9741666666666667</v>
       </c>
       <c r="G37">
-        <v>0.02029810899283661</v>
+        <v>0.04663317250389232</v>
       </c>
       <c r="H37">
-        <v>0.8946666666666667</v>
+        <v>0.9692307692307693</v>
       </c>
       <c r="I37">
-        <v>0.04266666666666665</v>
+        <v>0.03768445758127964</v>
       </c>
       <c r="J37">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="K37">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="L37">
-        <v>0.913800505050505</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="M37">
-        <v>0.05175830784892948</v>
+        <v>0.0244948974278318</v>
       </c>
       <c r="N37">
-        <v>0.8629166666666667</v>
+        <v>0.95</v>
       </c>
       <c r="O37">
-        <v>0.05211128879382172</v>
+        <v>0.06123724356957946</v>
       </c>
       <c r="P37">
-        <v>0.8781713865769595</v>
+        <v>0.9555555555555555</v>
       </c>
       <c r="Q37">
-        <v>0.05185520991559336</v>
+        <v>0.05443310539518176</v>
       </c>
       <c r="R37" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>0.95943158436214</v>
+        <v>0.9741666666666667</v>
       </c>
       <c r="G38">
-        <v>0.02002715089262896</v>
+        <v>0.0193020580365008</v>
       </c>
       <c r="H38">
-        <v>0.8783333333333333</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="I38">
-        <v>0.04688046264466447</v>
+        <v>0.04865042554105199</v>
       </c>
       <c r="J38">
-        <v>0.8441666666666666</v>
+        <v>0.925</v>
       </c>
       <c r="K38">
-        <v>0.04904292337670478</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="L38">
-        <v>0.9156096681096682</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="M38">
-        <v>0.05044792636295648</v>
+        <v>0.04196559437338058</v>
       </c>
       <c r="N38">
-        <v>0.8441666666666666</v>
+        <v>0.925</v>
       </c>
       <c r="O38">
-        <v>0.04904292337670478</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="P38">
-        <v>0.8620173986660055</v>
+        <v>0.9156132756132755</v>
       </c>
       <c r="Q38">
-        <v>0.04954598883520467</v>
+        <v>0.05528148886400736</v>
       </c>
       <c r="R38" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F39">
-        <v>0.9532201646090535</v>
+        <v>0.9691666666666666</v>
       </c>
       <c r="G39">
-        <v>0.01631057851068567</v>
+        <v>0.05960518247415889</v>
       </c>
       <c r="H39">
-        <v>0.8949999999999999</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="I39">
-        <v>0.03255764119219944</v>
+        <v>0.07536891516255934</v>
       </c>
       <c r="J39">
-        <v>0.8622222222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="K39">
-        <v>0.04756939375504197</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="L39">
-        <v>0.918169191919192</v>
+        <v>0.9375</v>
       </c>
       <c r="M39">
-        <v>0.01666735535767197</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="N39">
-        <v>0.8622222222222222</v>
+        <v>0.9375</v>
       </c>
       <c r="O39">
-        <v>0.04756939375504197</v>
+        <v>0.07905694150420949</v>
       </c>
       <c r="P39">
-        <v>0.8799582903336773</v>
+        <v>0.9312878787878788</v>
       </c>
       <c r="Q39">
-        <v>0.03289576245687116</v>
+        <v>0.08474005517658986</v>
       </c>
       <c r="R39" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2545,43 +2521,43 @@
         <v>29</v>
       </c>
       <c r="F40">
-        <v>0.9504359567901235</v>
+        <v>0.9689583333333334</v>
       </c>
       <c r="G40">
-        <v>0.01914220914008727</v>
+        <v>0.05340164895498186</v>
       </c>
       <c r="H40">
-        <v>0.8873333333333333</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="I40">
-        <v>0.02924228293261509</v>
+        <v>0.05756395979652217</v>
       </c>
       <c r="J40">
-        <v>0.8795833333333334</v>
+        <v>0.9425000000000001</v>
       </c>
       <c r="K40">
-        <v>0.02538515046631656</v>
+        <v>0.0687386354243376</v>
       </c>
       <c r="L40">
-        <v>0.8904942279942279</v>
+        <v>0.9358333333333334</v>
       </c>
       <c r="M40">
-        <v>0.03408099751317067</v>
+        <v>0.06930207628763931</v>
       </c>
       <c r="N40">
-        <v>0.8795833333333334</v>
+        <v>0.9425000000000001</v>
       </c>
       <c r="O40">
-        <v>0.02538515046631656</v>
+        <v>0.0687386354243376</v>
       </c>
       <c r="P40">
-        <v>0.8777473038657249</v>
+        <v>0.9358333333333334</v>
       </c>
       <c r="Q40">
-        <v>0.02493955165490187</v>
+        <v>0.06885527853923799</v>
       </c>
       <c r="R40" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2589,43 +2565,43 @@
         <v>30</v>
       </c>
       <c r="F41">
-        <v>0.9492618312757202</v>
+        <v>0.9689583333333334</v>
       </c>
       <c r="G41">
-        <v>0.03699249956018717</v>
+        <v>0.05340164895498186</v>
       </c>
       <c r="H41">
-        <v>0.9023333333333333</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="I41">
-        <v>0.06768883052452436</v>
+        <v>0.04865042554105199</v>
       </c>
       <c r="J41">
-        <v>0.8804166666666665</v>
+        <v>0.915</v>
       </c>
       <c r="K41">
-        <v>0.08098353742170898</v>
+        <v>0.06490377492873584</v>
       </c>
       <c r="L41">
-        <v>0.9115003052503052</v>
+        <v>0.9358333333333334</v>
       </c>
       <c r="M41">
-        <v>0.04535622806252892</v>
+        <v>0.06409628174343138</v>
       </c>
       <c r="N41">
-        <v>0.8804166666666665</v>
+        <v>0.915</v>
       </c>
       <c r="O41">
-        <v>0.08098353742170898</v>
+        <v>0.06490377492873584</v>
       </c>
       <c r="P41">
-        <v>0.8890646904694892</v>
+        <v>0.9184884559884559</v>
       </c>
       <c r="Q41">
-        <v>0.06777294191089615</v>
+        <v>0.06274755553546002</v>
       </c>
       <c r="R41" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -2633,43 +2609,43 @@
         <v>31</v>
       </c>
       <c r="F42">
-        <v>0.943371913580247</v>
+        <v>0.9666666666666666</v>
       </c>
       <c r="G42">
-        <v>0.03360332330505016</v>
+        <v>0.04656611190316171</v>
       </c>
       <c r="H42">
-        <v>0.8786666666666665</v>
+        <v>0.9076923076923077</v>
       </c>
       <c r="I42">
-        <v>0.04509742540076735</v>
+        <v>0.05756395979652219</v>
       </c>
       <c r="J42">
-        <v>0.8761111111111111</v>
+        <v>0.875</v>
       </c>
       <c r="K42">
-        <v>0.02704092120755296</v>
+        <v>0.06846531968814576</v>
       </c>
       <c r="L42">
-        <v>0.8833062770562771</v>
+        <v>0.9383333333333332</v>
       </c>
       <c r="M42">
-        <v>0.04861479544409806</v>
+        <v>0.03921096785339528</v>
       </c>
       <c r="N42">
-        <v>0.8761111111111111</v>
+        <v>0.875</v>
       </c>
       <c r="O42">
-        <v>0.02704092120755296</v>
+        <v>0.06846531968814576</v>
       </c>
       <c r="P42">
-        <v>0.8706260079789491</v>
+        <v>0.8881313131313131</v>
       </c>
       <c r="Q42">
-        <v>0.03652146176086825</v>
+        <v>0.06155273892704929</v>
       </c>
       <c r="R42" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2677,43 +2653,43 @@
         <v>32</v>
       </c>
       <c r="F43">
-        <v>0.9407767489711933</v>
+        <v>0.9608333333333334</v>
       </c>
       <c r="G43">
-        <v>0.03684629470689227</v>
+        <v>0.06300352723811932</v>
       </c>
       <c r="H43">
-        <v>0.8783333333333333</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="I43">
-        <v>0.04688046264466447</v>
+        <v>0.05756395979652217</v>
       </c>
       <c r="J43">
-        <v>0.8573611111111111</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="K43">
-        <v>0.0552013010895152</v>
+        <v>0.0686476510887299</v>
       </c>
       <c r="L43">
-        <v>0.8685101010101011</v>
+        <v>0.9441666666666666</v>
       </c>
       <c r="M43">
-        <v>0.03960783117360131</v>
+        <v>0.06900080514828151</v>
       </c>
       <c r="N43">
-        <v>0.8573611111111111</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="O43">
-        <v>0.0552013010895152</v>
+        <v>0.0686476510887299</v>
       </c>
       <c r="P43">
-        <v>0.8586797262764756</v>
+        <v>0.9397005772005773</v>
       </c>
       <c r="Q43">
-        <v>0.05180175890199754</v>
+        <v>0.06852442419524116</v>
       </c>
       <c r="R43" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -2721,43 +2697,43 @@
         <v>33</v>
       </c>
       <c r="F44">
-        <v>0.940326646090535</v>
+        <v>0.95</v>
       </c>
       <c r="G44">
-        <v>0.04017015655733045</v>
+        <v>0.0311804782231162</v>
       </c>
       <c r="H44">
-        <v>0.8703333333333333</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="I44">
-        <v>0.04227423696663386</v>
+        <v>0.04865042554105199</v>
       </c>
       <c r="J44">
-        <v>0.8698611111111111</v>
+        <v>0.925</v>
       </c>
       <c r="K44">
-        <v>0.03560705905183675</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="L44">
-        <v>0.8778174603174603</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="M44">
-        <v>0.0542000740052247</v>
+        <v>0.04196559437338058</v>
       </c>
       <c r="N44">
-        <v>0.8698611111111111</v>
+        <v>0.925</v>
       </c>
       <c r="O44">
-        <v>0.03560705905183675</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="P44">
-        <v>0.8650357232207078</v>
+        <v>0.9156132756132755</v>
       </c>
       <c r="Q44">
-        <v>0.04033014918150671</v>
+        <v>0.05528148886400736</v>
       </c>
       <c r="R44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -2765,43 +2741,43 @@
         <v>34</v>
       </c>
       <c r="F45">
-        <v>0.9197222222222223</v>
+        <v>0.95</v>
       </c>
       <c r="G45">
-        <v>0.01692343364421102</v>
+        <v>0.0311804782231162</v>
       </c>
       <c r="H45">
-        <v>0.8873333333333333</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="I45">
-        <v>0.02924228293261509</v>
+        <v>0.04865042554105199</v>
       </c>
       <c r="J45">
-        <v>0.8795833333333334</v>
+        <v>0.925</v>
       </c>
       <c r="K45">
-        <v>0.02538515046631656</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="L45">
-        <v>0.8904942279942279</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="M45">
-        <v>0.03408099751317067</v>
+        <v>0.04196559437338058</v>
       </c>
       <c r="N45">
-        <v>0.8795833333333334</v>
+        <v>0.925</v>
       </c>
       <c r="O45">
-        <v>0.02538515046631656</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="P45">
-        <v>0.8777473038657249</v>
+        <v>0.9156132756132755</v>
       </c>
       <c r="Q45">
-        <v>0.02493955165490187</v>
+        <v>0.05528148886400736</v>
       </c>
       <c r="R45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -2809,43 +2785,43 @@
         <v>35</v>
       </c>
       <c r="F46">
-        <v>0.9197222222222223</v>
+        <v>0.9433333333333334</v>
       </c>
       <c r="G46">
-        <v>0.01692343364421102</v>
+        <v>0.06183535486363049</v>
       </c>
       <c r="H46">
-        <v>0.8873333333333333</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="I46">
-        <v>0.02924228293261509</v>
+        <v>0.05756395979652217</v>
       </c>
       <c r="J46">
-        <v>0.8795833333333334</v>
+        <v>0.9275</v>
       </c>
       <c r="K46">
-        <v>0.02538515046631656</v>
+        <v>0.07348469228349534</v>
       </c>
       <c r="L46">
-        <v>0.8904942279942279</v>
+        <v>0.9425000000000001</v>
       </c>
       <c r="M46">
-        <v>0.03408099751317067</v>
+        <v>0.0687386354243376</v>
       </c>
       <c r="N46">
-        <v>0.8795833333333334</v>
+        <v>0.9275</v>
       </c>
       <c r="O46">
-        <v>0.02538515046631656</v>
+        <v>0.07348469228349534</v>
       </c>
       <c r="P46">
-        <v>0.8777473038657249</v>
+        <v>0.9291666666666668</v>
       </c>
       <c r="Q46">
-        <v>0.02493955165490187</v>
+        <v>0.07141644517879134</v>
       </c>
       <c r="R46" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -2853,43 +2829,43 @@
         <v>36</v>
       </c>
       <c r="F47">
-        <v>0.8541756687242799</v>
+        <v>0.9362499999999999</v>
       </c>
       <c r="G47">
-        <v>0.03737363161348328</v>
+        <v>0.03365985904770118</v>
       </c>
       <c r="H47">
-        <v>0.533</v>
+        <v>0.723076923076923</v>
       </c>
       <c r="I47">
-        <v>0.09693296652842107</v>
+        <v>0.1583943098613385</v>
       </c>
       <c r="J47">
-        <v>0.4102777777777778</v>
+        <v>0.6125</v>
       </c>
       <c r="K47">
-        <v>0.0858681608594403</v>
+        <v>0.2179449471770337</v>
       </c>
       <c r="L47">
-        <v>0.425632646339168</v>
+        <v>0.5848304473304473</v>
       </c>
       <c r="M47">
-        <v>0.1171188688822568</v>
+        <v>0.2287001060983311</v>
       </c>
       <c r="N47">
-        <v>0.4102777777777778</v>
+        <v>0.6125</v>
       </c>
       <c r="O47">
-        <v>0.0858681608594403</v>
+        <v>0.2179449471770337</v>
       </c>
       <c r="P47">
-        <v>0.3542030350066262</v>
+        <v>0.5770833333333332</v>
       </c>
       <c r="Q47">
-        <v>0.1037024172885547</v>
+        <v>0.2358645504686969</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -2897,43 +2873,43 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>0.7932407407407408</v>
+        <v>0.89</v>
       </c>
       <c r="G48">
-        <v>0.07951574543630217</v>
+        <v>0.07442371187255369</v>
       </c>
       <c r="H48">
-        <v>0.7413333333333333</v>
+        <v>0.8307692307692308</v>
       </c>
       <c r="I48">
-        <v>0.09855849926707377</v>
+        <v>0.1230769230769231</v>
       </c>
       <c r="J48">
-        <v>0.689861111111111</v>
+        <v>0.835</v>
       </c>
       <c r="K48">
-        <v>0.1192736181544533</v>
+        <v>0.1116355678088305</v>
       </c>
       <c r="L48">
-        <v>0.7361431623931624</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="M48">
-        <v>0.10431512412035</v>
+        <v>0.1226557966198273</v>
       </c>
       <c r="N48">
-        <v>0.689861111111111</v>
+        <v>0.835</v>
       </c>
       <c r="O48">
-        <v>0.1192736181544533</v>
+        <v>0.1116355678088305</v>
       </c>
       <c r="P48">
-        <v>0.6837571497130321</v>
+        <v>0.8262878787878787</v>
       </c>
       <c r="Q48">
-        <v>0.1241359354374842</v>
+        <v>0.129093382017801</v>
       </c>
       <c r="R48" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
